--- a/data/vadas.xlsx
+++ b/data/vadas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K247"/>
+  <dimension ref="A1:K249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>143149</v>
+        <v>160312</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -512,15 +512,15 @@
         <v>46273</v>
       </c>
       <c r="H2" t="n">
-        <v>47252</v>
+        <v>796144</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>BRACELL PAPEIS NORDESTE LTDA</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>46.37</v>
+        <v>208.72</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,19 +529,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>151456</v>
+        <v>160314</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -549,15 +549,15 @@
         <v>46273</v>
       </c>
       <c r="H3" t="n">
-        <v>789603</v>
+        <v>796144</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SOFTYS BRASIL LTDA</t>
+          <t>BRACELL PAPEIS NORDESTE LTDA</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>248.27</v>
+        <v>1461.04</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -566,19 +566,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>154018</v>
+        <v>163228</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -586,15 +586,15 @@
         <v>46273</v>
       </c>
       <c r="H4" t="n">
-        <v>794919</v>
+        <v>796144</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>BRACELL PAPEIS NORDESTE LTDA</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>21.06</v>
+        <v>587.88</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>160314</v>
+        <v>136634</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -623,15 +623,15 @@
         <v>46273</v>
       </c>
       <c r="H5" t="n">
-        <v>796144</v>
+        <v>30307</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BRACELL PAPEIS NORDESTE LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1461.04</v>
+        <v>231.6</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -640,19 +640,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>153154</v>
+        <v>163048</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -660,15 +660,15 @@
         <v>46273</v>
       </c>
       <c r="H6" t="n">
-        <v>5582</v>
+        <v>30307</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>50.1</v>
+        <v>189.96</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -681,15 +681,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27820</v>
+        <v>157145</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -697,15 +697,15 @@
         <v>46273</v>
       </c>
       <c r="H7" t="n">
-        <v>31305</v>
+        <v>796414</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LABORATORIO GLOBO LTDA</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>42.15</v>
+        <v>54.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -714,19 +714,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WESLEY DE OLIVEIRA PAZ</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>160714</v>
+        <v>148084</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -734,15 +734,15 @@
         <v>46273</v>
       </c>
       <c r="H8" t="n">
-        <v>31267</v>
+        <v>5582</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>EMS S/A</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>823.63</v>
+        <v>21.53</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -751,19 +751,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>140243</v>
+        <v>153154</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -771,15 +771,15 @@
         <v>46273</v>
       </c>
       <c r="H9" t="n">
-        <v>47252</v>
+        <v>5582</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>EMS S/A</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6.83</v>
+        <v>50.1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -788,19 +788,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>64866</v>
+        <v>154018</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -808,15 +808,15 @@
         <v>46273</v>
       </c>
       <c r="H10" t="n">
-        <v>31267</v>
+        <v>794919</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>EMS S/A</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>42.23</v>
+        <v>21.06</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -825,19 +825,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO CHAGAS </t>
+          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62448</v>
+        <v>156160</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -845,15 +845,15 @@
         <v>46273</v>
       </c>
       <c r="H11" t="n">
-        <v>793261</v>
+        <v>794319</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FARMAX DISTRIBUIDORA S.A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8.529999999999999</v>
+        <v>269.95</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -862,19 +862,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t xml:space="preserve">FRANCISCO CHAGAS </t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>144742</v>
+        <v>62448</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -882,15 +882,15 @@
         <v>46273</v>
       </c>
       <c r="H12" t="n">
-        <v>37273</v>
+        <v>793261</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LEGRAND PHARMA IND FARM LTDA</t>
+          <t>FARMAX DISTRIBUIDORA S.A</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>74.06999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -899,19 +899,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>161905</v>
+        <v>57096</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -919,15 +919,15 @@
         <v>46273</v>
       </c>
       <c r="H13" t="n">
-        <v>796383</v>
+        <v>33928</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>20.55</v>
+        <v>24.16</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -936,19 +936,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>148818</v>
+        <v>161905</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -956,15 +956,15 @@
         <v>46273</v>
       </c>
       <c r="H14" t="n">
-        <v>792019</v>
+        <v>796383</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TORRENT DO BRASIL LTDA</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7.08</v>
+        <v>20.55</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>139823</v>
+        <v>161906</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -993,15 +993,15 @@
         <v>46273</v>
       </c>
       <c r="H15" t="n">
-        <v>30083</v>
+        <v>796383</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>27.9</v>
+        <v>20.55</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1014,15 +1014,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>160024</v>
+        <v>17310</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1030,15 +1030,15 @@
         <v>46273</v>
       </c>
       <c r="H16" t="n">
-        <v>794671</v>
+        <v>47252</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>37.65</v>
+        <v>45.93</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1047,19 +1047,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17310</v>
+        <v>79375</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>45.93</v>
+        <v>11.63</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1084,19 +1084,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>161758</v>
+        <v>140243</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -1104,15 +1104,15 @@
         <v>46273</v>
       </c>
       <c r="H18" t="n">
-        <v>790283</v>
+        <v>47252</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PHARLAB INDUSTRIA FARMACEUTICA S.A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>31.35</v>
+        <v>6.83</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1121,19 +1121,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>136634</v>
+        <v>143149</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1141,15 +1141,15 @@
         <v>46273</v>
       </c>
       <c r="H19" t="n">
-        <v>30307</v>
+        <v>47252</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>231.6</v>
+        <v>46.37</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1162,15 +1162,15 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>126927</v>
+        <v>151933</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1178,15 +1178,15 @@
         <v>46273</v>
       </c>
       <c r="H20" t="n">
-        <v>30083</v>
+        <v>789423</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>24</v>
+        <v>96.89</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1195,19 +1195,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>163048</v>
+        <v>75370</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1215,15 +1215,15 @@
         <v>46273</v>
       </c>
       <c r="H21" t="n">
-        <v>30307</v>
+        <v>794365</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>189.96</v>
+        <v>18.96</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1232,19 +1232,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79375</v>
+        <v>27820</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -1252,15 +1252,15 @@
         <v>46273</v>
       </c>
       <c r="H22" t="n">
-        <v>47252</v>
+        <v>31305</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LABORATORIO GLOBO LTDA</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>11.63</v>
+        <v>42.15</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75370</v>
+        <v>140585</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1289,15 +1289,15 @@
         <v>46273</v>
       </c>
       <c r="H23" t="n">
-        <v>794365</v>
+        <v>30791</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>18.96</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1310,15 +1310,15 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>157145</v>
+        <v>992191</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1326,15 +1326,15 @@
         <v>46273</v>
       </c>
       <c r="H24" t="n">
-        <v>796414</v>
+        <v>30791</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>54.4</v>
+        <v>38.15</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1343,19 +1343,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>154723</v>
+        <v>60950</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1363,15 +1363,15 @@
         <v>46273</v>
       </c>
       <c r="H25" t="n">
-        <v>30083</v>
+        <v>37273</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>LEGRAND PHARMA IND FARM LTDA</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>64</v>
+        <v>89.55</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1380,19 +1380,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>992191</v>
+        <v>144742</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1400,15 +1400,15 @@
         <v>46273</v>
       </c>
       <c r="H26" t="n">
-        <v>30791</v>
+        <v>37273</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>LEGRAND PHARMA IND FARM LTDA</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>38.15</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1417,19 +1417,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
+          <t xml:space="preserve">FRANCISCO CHAGAS </t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>156160</v>
+        <v>155972</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -1437,15 +1437,15 @@
         <v>46273</v>
       </c>
       <c r="H27" t="n">
-        <v>794319</v>
+        <v>37273</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>LEGRAND PHARMA IND FARM LTDA</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>269.95</v>
+        <v>61.35</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1454,19 +1454,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>96164</v>
+        <v>126927</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
@@ -1474,15 +1474,15 @@
         <v>46273</v>
       </c>
       <c r="H28" t="n">
-        <v>33286</v>
+        <v>30083</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>29.84</v>
+        <v>24</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1491,19 +1491,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>163228</v>
+        <v>139823</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -1511,15 +1511,15 @@
         <v>46273</v>
       </c>
       <c r="H29" t="n">
-        <v>796144</v>
+        <v>30083</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>BRACELL PAPEIS NORDESTE LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>587.88</v>
+        <v>27.9</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1528,19 +1528,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>160312</v>
+        <v>154723</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1548,15 +1548,15 @@
         <v>46273</v>
       </c>
       <c r="H30" t="n">
-        <v>796144</v>
+        <v>30083</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>BRACELL PAPEIS NORDESTE LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>208.72</v>
+        <v>64</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1565,19 +1565,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>161906</v>
+        <v>96164</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1585,15 +1585,15 @@
         <v>46273</v>
       </c>
       <c r="H31" t="n">
-        <v>796383</v>
+        <v>33286</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>20.55</v>
+        <v>29.84</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1602,19 +1602,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>57096</v>
+        <v>161758</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1622,15 +1622,15 @@
         <v>46273</v>
       </c>
       <c r="H32" t="n">
-        <v>33928</v>
+        <v>790283</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>PHARLAB INDUSTRIA FARMACEUTICA S.A</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>24.16</v>
+        <v>31.35</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>139738</v>
+        <v>142425</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -1659,15 +1659,15 @@
         <v>46273</v>
       </c>
       <c r="H33" t="n">
-        <v>789525</v>
+        <v>789429</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>PRATI DONADUZZI &amp; CIA LTDA - PR</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>98.17</v>
+        <v>55.34</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1676,19 +1676,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18589</v>
+        <v>155661</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1696,15 +1696,15 @@
         <v>46273</v>
       </c>
       <c r="H34" t="n">
-        <v>789228</v>
+        <v>794671</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SANDOZ DO BRASI  IND. FARMAC LTDA (SP)</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>33.07</v>
+        <v>161.08</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1713,19 +1713,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>140585</v>
+        <v>160024</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -1733,15 +1733,15 @@
         <v>46273</v>
       </c>
       <c r="H35" t="n">
-        <v>30791</v>
+        <v>794671</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>72.09999999999999</v>
+        <v>37.65</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>151933</v>
+        <v>18589</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1770,15 +1770,15 @@
         <v>46273</v>
       </c>
       <c r="H36" t="n">
-        <v>789423</v>
+        <v>789228</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>SANDOZ DO BRASI  IND. FARMAC LTDA (SP)</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>96.89</v>
+        <v>33.07</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1787,19 +1787,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>60950</v>
+        <v>151456</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1807,15 +1807,15 @@
         <v>46273</v>
       </c>
       <c r="H37" t="n">
-        <v>37273</v>
+        <v>789603</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LEGRAND PHARMA IND FARM LTDA</t>
+          <t>SOFTYS BRASIL LTDA</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>89.55</v>
+        <v>248.27</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1824,19 +1824,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>148084</v>
+        <v>148818</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1844,15 +1844,15 @@
         <v>46273</v>
       </c>
       <c r="H38" t="n">
-        <v>5582</v>
+        <v>792019</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>TORRENT DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>21.53</v>
+        <v>7.08</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1861,19 +1861,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO CHAGAS </t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>155972</v>
+        <v>64866</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -1881,15 +1881,15 @@
         <v>46273</v>
       </c>
       <c r="H39" t="n">
-        <v>37273</v>
+        <v>31267</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LEGRAND PHARMA IND FARM LTDA</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>61.35</v>
+        <v>42.23</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1898,19 +1898,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>WESLEY DE OLIVEIRA PAZ</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>142425</v>
+        <v>160714</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1918,15 +1918,15 @@
         <v>46273</v>
       </c>
       <c r="H40" t="n">
-        <v>789429</v>
+        <v>31267</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PRATI DONADUZZI &amp; CIA LTDA - PR</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>55.34</v>
+        <v>823.63</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -1935,44 +1935,38 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUPERVISÃO HERTZ CE </t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>115223</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0000275143</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>46478</v>
-      </c>
+        <v>139738</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H41" t="n">
-        <v>789423</v>
+        <v>789525</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>98.17</v>
       </c>
       <c r="K41" t="n">
-        <v>20.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1990,7 +1984,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>161315</v>
+        <v>162979</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -1998,15 +1992,15 @@
         <v>46273</v>
       </c>
       <c r="H42" t="n">
-        <v>796383</v>
+        <v>793527</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>AGAPLASTIC INDUSTRIA E COMERCIO LTDA - AGPMED</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>16.69</v>
+        <v>31.57</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2015,19 +2009,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t xml:space="preserve">FRANCISCO CHAGAS </t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>139063</v>
+        <v>126056</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -2035,15 +2029,15 @@
         <v>46273</v>
       </c>
       <c r="H43" t="n">
-        <v>32816</v>
+        <v>790249</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DKT DO BRASIL PROD.DE USO PESS (PRUDENCE)</t>
+          <t>BLOWTEX - FABRICA DE ARTEFATOS DE LATEX BLOWTEX LTDA</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>12.27</v>
+        <v>1.79</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2052,19 +2046,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>146367</v>
+        <v>160312</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -2072,15 +2066,15 @@
         <v>46273</v>
       </c>
       <c r="H44" t="n">
-        <v>47252</v>
+        <v>796144</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>BRACELL PAPEIS NORDESTE LTDA</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>85.89</v>
+        <v>199.2</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2089,19 +2083,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>69302</v>
+        <v>160314</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -2109,15 +2103,15 @@
         <v>46273</v>
       </c>
       <c r="H45" t="n">
-        <v>47252</v>
+        <v>796144</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>BRACELL PAPEIS NORDESTE LTDA</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>612.55</v>
+        <v>199.2</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2126,19 +2120,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>146488</v>
+        <v>127181</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -2146,15 +2140,15 @@
         <v>46273</v>
       </c>
       <c r="H46" t="n">
-        <v>31305</v>
+        <v>796414</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LABORATORIO GLOBO LTDA</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>48.19</v>
+        <v>31.9</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2163,19 +2157,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>162867</v>
+        <v>153891</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -2183,15 +2177,15 @@
         <v>46273</v>
       </c>
       <c r="H47" t="n">
-        <v>792141</v>
+        <v>796414</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>228.71</v>
+        <v>32.68</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2204,15 +2198,15 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>117307</v>
+        <v>158708</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -2220,15 +2214,15 @@
         <v>46273</v>
       </c>
       <c r="H48" t="n">
-        <v>790808</v>
+        <v>796414</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>50.08</v>
+        <v>24.45</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2237,19 +2231,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>127181</v>
+        <v>139063</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2257,15 +2251,15 @@
         <v>46273</v>
       </c>
       <c r="H49" t="n">
-        <v>796414</v>
+        <v>32816</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>DKT DO BRASIL PROD.DE USO PESS (PRUDENCE)</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>31.9</v>
+        <v>12.27</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2286,7 +2280,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>79669</v>
+        <v>111759</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -2294,15 +2288,15 @@
         <v>46273</v>
       </c>
       <c r="H50" t="n">
-        <v>47252</v>
+        <v>33928</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>10.26</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2311,19 +2305,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>160026</v>
+        <v>144293</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -2331,15 +2325,15 @@
         <v>46273</v>
       </c>
       <c r="H51" t="n">
-        <v>794671</v>
+        <v>33928</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>150.6</v>
+        <v>15.31</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2348,19 +2342,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO CHAGAS </t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>126056</v>
+        <v>147203</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -2368,15 +2362,15 @@
         <v>46273</v>
       </c>
       <c r="H52" t="n">
-        <v>790249</v>
+        <v>33928</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>BLOWTEX - FABRICA DE ARTEFATOS DE LATEX BLOWTEX LTDA</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1.79</v>
+        <v>38.56</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2385,19 +2379,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>145831</v>
+        <v>162867</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
@@ -2405,15 +2399,15 @@
         <v>46273</v>
       </c>
       <c r="H53" t="n">
-        <v>30083</v>
+        <v>792141</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>43.88</v>
+        <v>228.71</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2426,15 +2420,15 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>147203</v>
+        <v>161315</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
@@ -2442,15 +2436,15 @@
         <v>46273</v>
       </c>
       <c r="H54" t="n">
-        <v>33928</v>
+        <v>796383</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>38.56</v>
+        <v>16.69</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2459,19 +2453,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>160314</v>
+        <v>69302</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -2479,15 +2473,15 @@
         <v>46273</v>
       </c>
       <c r="H55" t="n">
-        <v>796144</v>
+        <v>47252</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BRACELL PAPEIS NORDESTE LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>199.2</v>
+        <v>612.55</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2500,15 +2494,15 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>111759</v>
+        <v>79154</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -2516,15 +2510,15 @@
         <v>46273</v>
       </c>
       <c r="H56" t="n">
-        <v>33928</v>
+        <v>47252</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>20</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2533,19 +2527,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>54844</v>
+        <v>79243</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -2553,15 +2547,15 @@
         <v>46273</v>
       </c>
       <c r="H57" t="n">
-        <v>30791</v>
+        <v>47252</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>15.23</v>
+        <v>11.3</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2570,19 +2564,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>160312</v>
+        <v>79669</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
@@ -2590,15 +2584,15 @@
         <v>46273</v>
       </c>
       <c r="H58" t="n">
-        <v>796144</v>
+        <v>47252</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>BRACELL PAPEIS NORDESTE LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>199.2</v>
+        <v>10.26</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2619,7 +2613,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>79243</v>
+        <v>112003</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -2635,7 +2629,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>11.3</v>
+        <v>25.85</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2648,15 +2642,15 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>79154</v>
+        <v>146367</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -2672,7 +2666,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>9.140000000000001</v>
+        <v>85.89</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2681,19 +2675,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>162979</v>
+        <v>161224</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
@@ -2701,15 +2695,15 @@
         <v>46273</v>
       </c>
       <c r="H61" t="n">
-        <v>793527</v>
+        <v>47252</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AGAPLASTIC INDUSTRIA E COMERCIO LTDA - AGPMED</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>31.57</v>
+        <v>15.28</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2755,19 +2749,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>156054</v>
+        <v>152186</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
@@ -2775,15 +2769,15 @@
         <v>46273</v>
       </c>
       <c r="H63" t="n">
-        <v>789825</v>
+        <v>47252</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AIRELA INDUSTRIA FARMACEUTICA LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>17.72</v>
+        <v>29.03</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2792,56 +2786,62 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t xml:space="preserve">SUPERVISÃO HERTZ CE </t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>153891</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+        <v>115223</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0000275143</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46478</v>
+      </c>
       <c r="G64" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H64" t="n">
-        <v>796414</v>
+        <v>789423</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>32.68</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>152186</v>
+        <v>146488</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
@@ -2849,15 +2849,15 @@
         <v>46273</v>
       </c>
       <c r="H65" t="n">
-        <v>47252</v>
+        <v>31305</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LABORATORIO GLOBO LTDA</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>29.03</v>
+        <v>48.19</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2866,19 +2866,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>144293</v>
+        <v>54844</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
@@ -2886,15 +2886,15 @@
         <v>46273</v>
       </c>
       <c r="H66" t="n">
-        <v>33928</v>
+        <v>30791</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>15.31</v>
+        <v>15.23</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>158708</v>
+        <v>145831</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
@@ -2923,15 +2923,15 @@
         <v>46273</v>
       </c>
       <c r="H67" t="n">
-        <v>796414</v>
+        <v>30083</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>24.45</v>
+        <v>43.88</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -2940,19 +2940,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>161224</v>
+        <v>117307</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
@@ -2960,15 +2960,15 @@
         <v>46273</v>
       </c>
       <c r="H68" t="n">
-        <v>47252</v>
+        <v>790808</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>15.28</v>
+        <v>50.08</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -2977,19 +2977,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>112003</v>
+        <v>160026</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
@@ -2997,15 +2997,15 @@
         <v>46273</v>
       </c>
       <c r="H69" t="n">
-        <v>47252</v>
+        <v>794671</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>25.85</v>
+        <v>150.6</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3014,105 +3014,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>115967</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>A05C00125</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>46388</v>
-      </c>
+        <v>156054</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H70" t="n">
-        <v>31305</v>
+        <v>789825</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LABORATORIO GLOBO LTDA</t>
+          <t>AIRELA INDUSTRIA FARMACEUTICA LTDA</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>17.72</v>
       </c>
       <c r="K70" t="n">
-        <v>31.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>139865</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2500455</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>46419</v>
-      </c>
+        <v>163574</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H71" t="n">
-        <v>794365</v>
+        <v>796834</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>BD - BECTON DICKINSON INDUSTRIAS CIRURGICAS LTDA</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K71" t="n">
-        <v>34.34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>163047</v>
+        <v>136630</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -3128,7 +3116,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>189.96</v>
+        <v>871.4400000000001</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3137,19 +3125,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>153437</v>
+        <v>136635</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
@@ -3157,15 +3145,15 @@
         <v>46273</v>
       </c>
       <c r="H73" t="n">
-        <v>793667</v>
+        <v>30307</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>LEBON PROD QUIM E FARMACEUTICOS LTDA EPP</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>223.43</v>
+        <v>166.74</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3174,19 +3162,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>145834</v>
+        <v>163047</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
@@ -3194,15 +3182,15 @@
         <v>46273</v>
       </c>
       <c r="H74" t="n">
-        <v>30083</v>
+        <v>30307</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>45.94</v>
+        <v>189.96</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3211,19 +3199,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>64769</v>
+        <v>163049</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -3231,15 +3219,15 @@
         <v>46273</v>
       </c>
       <c r="H75" t="n">
-        <v>31267</v>
+        <v>30307</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>4.93</v>
+        <v>189.96</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3260,7 +3248,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>153134</v>
+        <v>50407</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
@@ -3268,15 +3256,15 @@
         <v>46273</v>
       </c>
       <c r="H76" t="n">
-        <v>31267</v>
+        <v>794468</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>CELLERA CONSUMO LTDA (ES)</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>16.99</v>
+        <v>54.88</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3285,19 +3273,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>77100</v>
+        <v>155716</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
@@ -3305,15 +3293,15 @@
         <v>46273</v>
       </c>
       <c r="H77" t="n">
-        <v>794365</v>
+        <v>33766</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>CIFARMA CIENTIFICA FARMACEUTICA LTDA</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>15.67</v>
+        <v>11.1</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3326,15 +3314,15 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>147940</v>
+        <v>152143</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
@@ -3342,15 +3330,15 @@
         <v>46273</v>
       </c>
       <c r="H78" t="n">
-        <v>5582</v>
+        <v>796414</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>14.22</v>
+        <v>14.55</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3359,19 +3347,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>136635</v>
+        <v>147702</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
@@ -3379,15 +3367,15 @@
         <v>46273</v>
       </c>
       <c r="H79" t="n">
-        <v>30307</v>
+        <v>5582</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>EMS S/A</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>166.74</v>
+        <v>53.81</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3408,7 +3396,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>184</v>
+        <v>147940</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
@@ -3416,15 +3404,15 @@
         <v>46273</v>
       </c>
       <c r="H80" t="n">
-        <v>55</v>
+        <v>5582</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>IMEC- INDUSTRIA DE MEDICAMENTOS CUSTODIA LTDA</t>
+          <t>EMS S/A</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>73.42</v>
+        <v>14.22</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3433,19 +3421,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>161320</v>
+        <v>153947</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
@@ -3453,15 +3441,15 @@
         <v>46273</v>
       </c>
       <c r="H81" t="n">
-        <v>796383</v>
+        <v>794319</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>18.67</v>
+        <v>267.91</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3474,15 +3462,15 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>125</v>
+        <v>6</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t xml:space="preserve">FRANCISCO CHAGAS </t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>80756</v>
+        <v>143153</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
@@ -3490,15 +3478,15 @@
         <v>46273</v>
       </c>
       <c r="H82" t="n">
-        <v>47252</v>
+        <v>793261</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>FARMAX DISTRIBUIDORA S.A</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>6.02</v>
+        <v>10.09</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3511,15 +3499,15 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t xml:space="preserve">FRANCISCO CHAGAS </t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>155716</v>
+        <v>157716</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
@@ -3527,15 +3515,15 @@
         <v>46273</v>
       </c>
       <c r="H83" t="n">
-        <v>33766</v>
+        <v>793261</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CIFARMA CIENTIFICA FARMACEUTICA LTDA</t>
+          <t>FARMAX DISTRIBUIDORA S.A</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>11.1</v>
+        <v>31.29</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3548,15 +3536,15 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO CHAGAS </t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>153086</v>
+        <v>40380</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
@@ -3564,15 +3552,15 @@
         <v>46273</v>
       </c>
       <c r="H84" t="n">
-        <v>793535</v>
+        <v>33928</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>KANECHOM - SNC INDUSTRIA DE COSMETICOS LTDA</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>9.69</v>
+        <v>18.81</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3581,19 +3569,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>136630</v>
+        <v>63428</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -3601,15 +3589,15 @@
         <v>46273</v>
       </c>
       <c r="H85" t="n">
-        <v>30307</v>
+        <v>33928</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>871.4400000000001</v>
+        <v>20.73</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3618,19 +3606,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>16101</v>
+        <v>156106</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
@@ -3638,15 +3626,15 @@
         <v>46273</v>
       </c>
       <c r="H86" t="n">
-        <v>47252</v>
+        <v>792141</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>49.14</v>
+        <v>60.99</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3655,19 +3643,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>151934</v>
+        <v>160882</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
@@ -3675,15 +3663,15 @@
         <v>46273</v>
       </c>
       <c r="H87" t="n">
-        <v>789423</v>
+        <v>792141</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>96.89</v>
+        <v>104.71</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3704,7 +3692,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>143247</v>
+        <v>161316</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
@@ -3712,15 +3700,15 @@
         <v>46273</v>
       </c>
       <c r="H88" t="n">
-        <v>30083</v>
+        <v>796383</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>56.94</v>
+        <v>18.67</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3733,15 +3721,15 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>55000</v>
+        <v>161320</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
@@ -3749,15 +3737,15 @@
         <v>46273</v>
       </c>
       <c r="H89" t="n">
-        <v>30791</v>
+        <v>796383</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>70.3</v>
+        <v>18.67</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3778,7 +3766,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>50407</v>
+        <v>16101</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -3786,15 +3774,15 @@
         <v>46273</v>
       </c>
       <c r="H90" t="n">
-        <v>794468</v>
+        <v>47252</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CELLERA CONSUMO LTDA (ES)</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>54.88</v>
+        <v>49.14</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3803,19 +3791,19 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>156106</v>
+        <v>74608</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -3823,15 +3811,15 @@
         <v>46273</v>
       </c>
       <c r="H91" t="n">
-        <v>792141</v>
+        <v>47252</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>60.99</v>
+        <v>109.22</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -3840,19 +3828,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LOUIZE VANIELLE R. FARIAS (HNB RMR - PE)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>153947</v>
+        <v>79510</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
@@ -3860,15 +3848,15 @@
         <v>46273</v>
       </c>
       <c r="H92" t="n">
-        <v>794319</v>
+        <v>47252</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>267.91</v>
+        <v>17.9</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -3877,19 +3865,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>63428</v>
+        <v>80756</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
@@ -3897,15 +3885,15 @@
         <v>46273</v>
       </c>
       <c r="H93" t="n">
-        <v>33928</v>
+        <v>47252</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>20.73</v>
+        <v>6.02</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -3914,19 +3902,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>160222</v>
+        <v>148628</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
@@ -3934,15 +3922,15 @@
         <v>46273</v>
       </c>
       <c r="H94" t="n">
-        <v>796097</v>
+        <v>47252</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>VIDORA FILIAL</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>13.61</v>
+        <v>17.74</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -3955,15 +3943,15 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO CHAGAS </t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>157716</v>
+        <v>154575</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
@@ -3971,15 +3959,15 @@
         <v>46273</v>
       </c>
       <c r="H95" t="n">
-        <v>793261</v>
+        <v>47252</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>FARMAX DISTRIBUIDORA S.A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>31.29</v>
+        <v>49.02</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -3988,19 +3976,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>147702</v>
+        <v>184</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
@@ -4008,15 +3996,15 @@
         <v>46273</v>
       </c>
       <c r="H96" t="n">
-        <v>5582</v>
+        <v>55</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>IMEC- INDUSTRIA DE MEDICAMENTOS CUSTODIA LTDA</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>53.81</v>
+        <v>73.42</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4025,19 +4013,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t xml:space="preserve">FRANCISCO CHAGAS </t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>135323</v>
+        <v>153086</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
@@ -4045,15 +4033,15 @@
         <v>46273</v>
       </c>
       <c r="H97" t="n">
-        <v>30083</v>
+        <v>793535</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>KANECHOM - SNC INDUSTRIA DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>49.03</v>
+        <v>9.69</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4062,19 +4050,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>163049</v>
+        <v>151934</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
@@ -4082,15 +4070,15 @@
         <v>46273</v>
       </c>
       <c r="H98" t="n">
-        <v>30307</v>
+        <v>789423</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>189.96</v>
+        <v>96.89</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4111,7 +4099,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12874</v>
+        <v>77100</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
@@ -4119,15 +4107,15 @@
         <v>46273</v>
       </c>
       <c r="H99" t="n">
-        <v>31305</v>
+        <v>794365</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>LABORATORIO GLOBO LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>38</v>
+        <v>15.67</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4136,38 +4124,44 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>161316</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+        <v>139865</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2500455</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46419</v>
+      </c>
       <c r="G100" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H100" t="n">
-        <v>796383</v>
+        <v>794365</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>18.67</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="101">
@@ -4177,15 +4171,15 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>152143</v>
+        <v>12874</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
@@ -4193,15 +4187,15 @@
         <v>46273</v>
       </c>
       <c r="H101" t="n">
-        <v>796414</v>
+        <v>31305</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>LABORATORIO GLOBO LTDA</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>14.55</v>
+        <v>38</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4210,56 +4204,62 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>110</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+        <v>115967</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>A05C00125</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46388</v>
+      </c>
       <c r="G102" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H102" t="n">
-        <v>30083</v>
+        <v>31305</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>LABORATORIO GLOBO LTDA</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>15.58</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO CHAGAS </t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>143153</v>
+        <v>55000</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
@@ -4267,15 +4267,15 @@
         <v>46273</v>
       </c>
       <c r="H103" t="n">
-        <v>793261</v>
+        <v>30791</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>FARMAX DISTRIBUIDORA S.A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>10.09</v>
+        <v>70.3</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4284,19 +4284,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>163574</v>
+        <v>153437</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
@@ -4304,15 +4304,15 @@
         <v>46273</v>
       </c>
       <c r="H104" t="n">
-        <v>796834</v>
+        <v>793667</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>BD - BECTON DICKINSON INDUSTRIAS CIRURGICAS LTDA</t>
+          <t>LEBON PROD QUIM E FARMACEUTICOS LTDA EPP</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>0.04</v>
+        <v>223.43</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4321,19 +4321,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>148628</v>
+        <v>110</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
@@ -4341,15 +4341,15 @@
         <v>46273</v>
       </c>
       <c r="H105" t="n">
-        <v>47252</v>
+        <v>30083</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>17.74</v>
+        <v>15.58</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4362,15 +4362,15 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>154955</v>
+        <v>135323</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
@@ -4378,15 +4378,15 @@
         <v>46273</v>
       </c>
       <c r="H106" t="n">
-        <v>789525</v>
+        <v>30083</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>61.75</v>
+        <v>49.03</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4395,19 +4395,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>79510</v>
+        <v>143247</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
@@ -4415,15 +4415,15 @@
         <v>46273</v>
       </c>
       <c r="H107" t="n">
-        <v>47252</v>
+        <v>30083</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>17.9</v>
+        <v>56.94</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4436,15 +4436,15 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>80594</v>
+        <v>145834</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
@@ -4452,15 +4452,15 @@
         <v>46273</v>
       </c>
       <c r="H108" t="n">
-        <v>789525</v>
+        <v>30083</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>9.75</v>
+        <v>45.94</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4469,19 +4469,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>154575</v>
+        <v>42935</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
@@ -4489,15 +4489,15 @@
         <v>46273</v>
       </c>
       <c r="H109" t="n">
-        <v>47252</v>
+        <v>33286</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>49.02</v>
+        <v>189.06</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4506,19 +4506,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>40380</v>
+        <v>160222</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
@@ -4526,15 +4526,15 @@
         <v>46273</v>
       </c>
       <c r="H110" t="n">
-        <v>33928</v>
+        <v>796097</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>VIDORA FILIAL</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>18.81</v>
+        <v>13.61</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>151901</v>
+        <v>64769</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
@@ -4563,15 +4563,15 @@
         <v>46273</v>
       </c>
       <c r="H111" t="n">
-        <v>793186</v>
+        <v>31267</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ACCUMED PRODUTOS MEDICO HOSPITALARES LTDA</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>262.64</v>
+        <v>4.93</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4580,19 +4580,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>160882</v>
+        <v>153134</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
@@ -4600,15 +4600,15 @@
         <v>46273</v>
       </c>
       <c r="H112" t="n">
-        <v>792141</v>
+        <v>31267</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>104.71</v>
+        <v>16.99</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4617,19 +4617,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>74608</v>
+        <v>151901</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
@@ -4637,15 +4637,15 @@
         <v>46273</v>
       </c>
       <c r="H113" t="n">
-        <v>47252</v>
+        <v>793186</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>ACCUMED PRODUTOS MEDICO HOSPITALARES LTDA</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>109.22</v>
+        <v>262.64</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>139894</v>
+        <v>80594</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>98.65000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>42935</v>
+        <v>139894</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
@@ -4711,15 +4711,15 @@
         <v>46273</v>
       </c>
       <c r="H115" t="n">
-        <v>33286</v>
+        <v>789525</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>189.06</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4728,62 +4728,56 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>83003</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>4S6913</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>46447</v>
-      </c>
+        <v>154955</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H116" t="n">
-        <v>790808</v>
+        <v>789525</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>61.75</v>
       </c>
       <c r="K116" t="n">
-        <v>17.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>136633</v>
+        <v>160313</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
@@ -4791,15 +4785,15 @@
         <v>46273</v>
       </c>
       <c r="H117" t="n">
-        <v>30307</v>
+        <v>796144</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>BRACELL PAPEIS NORDESTE LTDA</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>166.74</v>
+        <v>208.72</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -4808,19 +4802,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>139771</v>
+        <v>136633</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
@@ -4828,15 +4822,15 @@
         <v>46273</v>
       </c>
       <c r="H118" t="n">
-        <v>47252</v>
+        <v>30307</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>44.57</v>
+        <v>166.74</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -4849,11 +4843,11 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4886,11 +4880,11 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4919,19 +4913,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>61913</v>
+        <v>139702</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
@@ -4939,15 +4933,15 @@
         <v>46273</v>
       </c>
       <c r="H121" t="n">
-        <v>33928</v>
+        <v>796414</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>21.17</v>
+        <v>38.28</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -4956,19 +4950,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>97314</v>
+        <v>157146</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
@@ -4976,15 +4970,15 @@
         <v>46273</v>
       </c>
       <c r="H122" t="n">
-        <v>793120</v>
+        <v>796414</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>127.07</v>
+        <v>43.58</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -4993,19 +4987,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>143207</v>
+        <v>61913</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
@@ -5013,15 +5007,15 @@
         <v>46273</v>
       </c>
       <c r="H123" t="n">
-        <v>47252</v>
+        <v>33928</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>227.76</v>
+        <v>21.17</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5042,7 +5036,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>132620</v>
+        <v>161311</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
@@ -5050,15 +5044,15 @@
         <v>46273</v>
       </c>
       <c r="H124" t="n">
-        <v>30083</v>
+        <v>796383</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>41.5</v>
+        <v>49.33</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5067,19 +5061,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>160313</v>
+        <v>161319</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
@@ -5087,15 +5081,15 @@
         <v>46273</v>
       </c>
       <c r="H125" t="n">
-        <v>796144</v>
+        <v>796383</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>BRACELL PAPEIS NORDESTE LTDA</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>208.72</v>
+        <v>16.69</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5108,15 +5102,15 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>147094</v>
+        <v>79553</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
@@ -5132,7 +5126,7 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>151.73</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5141,19 +5135,19 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>132425</v>
+        <v>139771</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
@@ -5161,15 +5155,15 @@
         <v>46273</v>
       </c>
       <c r="H127" t="n">
-        <v>30083</v>
+        <v>47252</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>41.5</v>
+        <v>44.57</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5178,19 +5172,19 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>161319</v>
+        <v>143207</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
@@ -5198,15 +5192,15 @@
         <v>46273</v>
       </c>
       <c r="H128" t="n">
-        <v>796383</v>
+        <v>47252</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>16.69</v>
+        <v>227.76</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5215,19 +5209,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>139929</v>
+        <v>147094</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
@@ -5235,15 +5229,15 @@
         <v>46273</v>
       </c>
       <c r="H129" t="n">
-        <v>789525</v>
+        <v>47252</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>91.67</v>
+        <v>151.73</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5252,19 +5246,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>139702</v>
+        <v>155477</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
@@ -5272,15 +5266,15 @@
         <v>46273</v>
       </c>
       <c r="H130" t="n">
-        <v>796414</v>
+        <v>47252</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>38.28</v>
+        <v>46.19</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5289,19 +5283,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>79553</v>
+        <v>155541</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
@@ -5317,7 +5311,7 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>9.119999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5326,19 +5320,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>156217</v>
+        <v>97314</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
@@ -5346,15 +5340,15 @@
         <v>46273</v>
       </c>
       <c r="H132" t="n">
-        <v>795043</v>
+        <v>793120</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>MUNILA DESENVOLVEDORA DE PROJETOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>30.18</v>
+        <v>127.07</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5363,19 +5357,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>155477</v>
+        <v>132425</v>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
@@ -5383,15 +5377,15 @@
         <v>46273</v>
       </c>
       <c r="H133" t="n">
-        <v>47252</v>
+        <v>30083</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>46.19</v>
+        <v>41.5</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5412,7 +5406,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>161311</v>
+        <v>132620</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
@@ -5420,15 +5414,15 @@
         <v>46273</v>
       </c>
       <c r="H134" t="n">
-        <v>796383</v>
+        <v>30083</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>49.33</v>
+        <v>41.5</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5437,56 +5431,62 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>157146</v>
-      </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+        <v>83003</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>4S6913</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>46447</v>
+      </c>
       <c r="G135" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H135" t="n">
-        <v>796414</v>
+        <v>790808</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>43.58</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>17.35</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>155541</v>
+        <v>156217</v>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
@@ -5494,15 +5494,15 @@
         <v>46273</v>
       </c>
       <c r="H136" t="n">
-        <v>47252</v>
+        <v>795043</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>MUNILA DESENVOLVEDORA DE PROJETOS LTDA</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>60.7</v>
+        <v>30.18</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5511,19 +5511,19 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>141557</v>
+        <v>139929</v>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
@@ -5531,15 +5531,15 @@
         <v>46273</v>
       </c>
       <c r="H137" t="n">
-        <v>31267</v>
+        <v>789525</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>133.69</v>
+        <v>91.67</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5548,19 +5548,19 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>154121</v>
+        <v>163084</v>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
@@ -5568,15 +5568,15 @@
         <v>46273</v>
       </c>
       <c r="H138" t="n">
-        <v>794919</v>
+        <v>796834</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>BD - BECTON DICKINSON INDUSTRIAS CIRURGICAS LTDA</t>
         </is>
       </c>
       <c r="J138" t="n">
-        <v>55.68</v>
+        <v>0.01</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5589,15 +5589,15 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>17256</v>
+        <v>146036</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
@@ -5605,15 +5605,15 @@
         <v>46273</v>
       </c>
       <c r="H139" t="n">
-        <v>47252</v>
+        <v>796414</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>113.23</v>
+        <v>54.4</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>4839</v>
+        <v>154121</v>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
@@ -5642,15 +5642,15 @@
         <v>46273</v>
       </c>
       <c r="H140" t="n">
-        <v>30791</v>
+        <v>794919</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>EMS S/A</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>25.83</v>
+        <v>55.68</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>162446</v>
+        <v>138898</v>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
@@ -5679,15 +5679,15 @@
         <v>46273</v>
       </c>
       <c r="H141" t="n">
-        <v>789423</v>
+        <v>33928</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>57.54</v>
+        <v>34.9</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5696,19 +5696,19 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t xml:space="preserve">FRANCISCO CHAGAS </t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>148818</v>
+        <v>155041</v>
       </c>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
@@ -5716,15 +5716,15 @@
         <v>46273</v>
       </c>
       <c r="H142" t="n">
-        <v>792019</v>
+        <v>792141</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>TORRENT DO BRASIL LTDA</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5774,15 +5774,15 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO CHAGAS </t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>155041</v>
+        <v>10464</v>
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
@@ -5790,15 +5790,15 @@
         <v>46273</v>
       </c>
       <c r="H144" t="n">
-        <v>792141</v>
+        <v>47252</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>41.9</v>
+        <v>6.95</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -5811,15 +5811,15 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>146036</v>
+        <v>17256</v>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
@@ -5827,15 +5827,15 @@
         <v>46273</v>
       </c>
       <c r="H145" t="n">
-        <v>796414</v>
+        <v>47252</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>54.4</v>
+        <v>113.23</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -5844,19 +5844,19 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>142905</v>
+        <v>19615</v>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
@@ -5864,15 +5864,15 @@
         <v>46273</v>
       </c>
       <c r="H146" t="n">
-        <v>30791</v>
+        <v>47252</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J146" t="n">
-        <v>33.35</v>
+        <v>9.26</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -5881,19 +5881,19 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>160025</v>
+        <v>79367</v>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
@@ -5901,15 +5901,15 @@
         <v>46273</v>
       </c>
       <c r="H147" t="n">
-        <v>794671</v>
+        <v>47252</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>75.3</v>
+        <v>10.23</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -5922,15 +5922,15 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>163084</v>
+        <v>110248</v>
       </c>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
@@ -5938,15 +5938,15 @@
         <v>46273</v>
       </c>
       <c r="H148" t="n">
-        <v>796834</v>
+        <v>47252</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>BD - BECTON DICKINSON INDUSTRIAS CIRURGICAS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>0.01</v>
+        <v>44.41</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -5992,19 +5992,19 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>138898</v>
+        <v>148277</v>
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
@@ -6012,15 +6012,15 @@
         <v>46273</v>
       </c>
       <c r="H150" t="n">
-        <v>33928</v>
+        <v>47252</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>34.9</v>
+        <v>15.97</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -6066,19 +6066,19 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>79367</v>
+        <v>162446</v>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
@@ -6086,15 +6086,15 @@
         <v>46273</v>
       </c>
       <c r="H152" t="n">
-        <v>47252</v>
+        <v>789423</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J152" t="n">
-        <v>10.23</v>
+        <v>57.54</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -6107,15 +6107,15 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>148277</v>
+        <v>4839</v>
       </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
@@ -6123,15 +6123,15 @@
         <v>46273</v>
       </c>
       <c r="H153" t="n">
-        <v>47252</v>
+        <v>30791</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>15.97</v>
+        <v>25.83</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -6140,19 +6140,19 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>19615</v>
+        <v>142905</v>
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
@@ -6160,15 +6160,15 @@
         <v>46273</v>
       </c>
       <c r="H154" t="n">
-        <v>47252</v>
+        <v>30791</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>9.26</v>
+        <v>33.35</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -6177,19 +6177,19 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>10464</v>
+        <v>160025</v>
       </c>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
@@ -6197,15 +6197,15 @@
         <v>46273</v>
       </c>
       <c r="H155" t="n">
-        <v>47252</v>
+        <v>794671</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>6.95</v>
+        <v>75.3</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -6214,19 +6214,19 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>110248</v>
+        <v>148818</v>
       </c>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
@@ -6234,15 +6234,15 @@
         <v>46273</v>
       </c>
       <c r="H156" t="n">
-        <v>47252</v>
+        <v>792019</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>TORRENT DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>44.41</v>
+        <v>42.1</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -6251,44 +6251,38 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>21130</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>FKP07321</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>46478</v>
-      </c>
+        <v>141557</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H157" t="n">
-        <v>789661</v>
+        <v>31267</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>SANOFI MEDLEY FARMACEUTICA LTDA</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>133.69</v>
       </c>
       <c r="K157" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6298,58 +6292,52 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>154949</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>2506277</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>46539</v>
-      </c>
+        <v>39799</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H158" t="n">
-        <v>789525</v>
+        <v>2378</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>BELFAR LTDA</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K158" t="n">
-        <v>40.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>82694</v>
+        <v>163049</v>
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
@@ -6357,15 +6345,15 @@
         <v>46273</v>
       </c>
       <c r="H159" t="n">
-        <v>47252</v>
+        <v>30307</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>5.48</v>
+        <v>189.96</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -6386,7 +6374,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>145832</v>
+        <v>134698</v>
       </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
@@ -6394,15 +6382,15 @@
         <v>46273</v>
       </c>
       <c r="H160" t="n">
-        <v>30083</v>
+        <v>796414</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>58.5</v>
+        <v>61.91</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -6411,19 +6399,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>152357</v>
+        <v>139700</v>
       </c>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
@@ -6431,15 +6419,15 @@
         <v>46273</v>
       </c>
       <c r="H161" t="n">
-        <v>47252</v>
+        <v>796414</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>10.59</v>
+        <v>32.68</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -6448,19 +6436,19 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>160714</v>
+        <v>158709</v>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
@@ -6468,15 +6456,15 @@
         <v>46273</v>
       </c>
       <c r="H162" t="n">
-        <v>31267</v>
+        <v>796414</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>2855.24</v>
+        <v>24.45</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -6485,19 +6473,19 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>151755</v>
+        <v>153154</v>
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
@@ -6505,15 +6493,15 @@
         <v>46273</v>
       </c>
       <c r="H163" t="n">
-        <v>789423</v>
+        <v>5582</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>EMS S/A</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>92.16</v>
+        <v>54.33</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -6522,19 +6510,19 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>39799</v>
+        <v>153947</v>
       </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
@@ -6542,15 +6530,15 @@
         <v>46273</v>
       </c>
       <c r="H164" t="n">
-        <v>2378</v>
+        <v>794319</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>BELFAR LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>68.98999999999999</v>
+        <v>150.22</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -6571,7 +6559,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>139991</v>
+        <v>162220</v>
       </c>
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr"/>
@@ -6579,15 +6567,15 @@
         <v>46273</v>
       </c>
       <c r="H165" t="n">
-        <v>794365</v>
+        <v>794223</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>FALCON DISTRIBUICAO ARMAZENAMENTO E TRANSPORTES SA - ONTEX</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>11.67</v>
+        <v>146.76</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -6608,7 +6596,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>142173</v>
+        <v>16101</v>
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
@@ -6624,7 +6612,7 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>76.81999999999999</v>
+        <v>15.35</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -6633,19 +6621,19 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>97616</v>
+        <v>82694</v>
       </c>
       <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr"/>
@@ -6653,15 +6641,15 @@
         <v>46273</v>
       </c>
       <c r="H167" t="n">
-        <v>33057</v>
+        <v>47252</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>NATULAB LABORATORIO LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>23.04</v>
+        <v>5.48</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -6711,15 +6699,15 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>113743</v>
+        <v>110329</v>
       </c>
       <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr"/>
@@ -6727,15 +6715,15 @@
         <v>46273</v>
       </c>
       <c r="H169" t="n">
-        <v>31267</v>
+        <v>47252</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>7.87</v>
+        <v>11.59</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -6756,7 +6744,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>18589</v>
+        <v>132982</v>
       </c>
       <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr"/>
@@ -6764,15 +6752,15 @@
         <v>46273</v>
       </c>
       <c r="H170" t="n">
-        <v>789228</v>
+        <v>47252</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SANDOZ DO BRASI  IND. FARMAC LTDA (SP)</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>11.85</v>
+        <v>185.83</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -6781,19 +6769,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>110329</v>
+        <v>139213</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
@@ -6809,7 +6797,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>11.59</v>
+        <v>127.11</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -6818,19 +6806,19 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>139721</v>
+        <v>142173</v>
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
@@ -6838,15 +6826,15 @@
         <v>46273</v>
       </c>
       <c r="H172" t="n">
-        <v>789525</v>
+        <v>47252</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>118.72</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -6859,15 +6847,15 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>162220</v>
+        <v>152357</v>
       </c>
       <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr"/>
@@ -6875,15 +6863,15 @@
         <v>46273</v>
       </c>
       <c r="H173" t="n">
-        <v>794223</v>
+        <v>47252</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>FALCON DISTRIBUICAO ARMAZENAMENTO E TRANSPORTES SA - ONTEX</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>146.76</v>
+        <v>10.59</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -6896,15 +6884,15 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>136048</v>
+        <v>154573</v>
       </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
@@ -6912,15 +6900,15 @@
         <v>46273</v>
       </c>
       <c r="H174" t="n">
-        <v>30083</v>
+        <v>47252</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>41.08</v>
+        <v>53.35</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -6929,19 +6917,19 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>153947</v>
+        <v>161224</v>
       </c>
       <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
@@ -6949,15 +6937,15 @@
         <v>46273</v>
       </c>
       <c r="H175" t="n">
-        <v>794319</v>
+        <v>47252</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>150.22</v>
+        <v>17.75</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -6978,7 +6966,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>59935</v>
+        <v>105228</v>
       </c>
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr"/>
@@ -6986,15 +6974,15 @@
         <v>46273</v>
       </c>
       <c r="H176" t="n">
-        <v>33286</v>
+        <v>789423</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>36.59</v>
+        <v>44.4</v>
       </c>
       <c r="K176" t="n">
         <v>0</v>
@@ -7007,15 +6995,15 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>158709</v>
+        <v>151755</v>
       </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
@@ -7023,15 +7011,15 @@
         <v>46273</v>
       </c>
       <c r="H177" t="n">
-        <v>796414</v>
+        <v>789423</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>24.45</v>
+        <v>92.16</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -7040,19 +7028,19 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>152613</v>
+        <v>139991</v>
       </c>
       <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
@@ -7060,15 +7048,15 @@
         <v>46273</v>
       </c>
       <c r="H178" t="n">
-        <v>30791</v>
+        <v>794365</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>106.83</v>
+        <v>11.67</v>
       </c>
       <c r="K178" t="n">
         <v>0</v>
@@ -7077,19 +7065,19 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>16101</v>
+        <v>76180</v>
       </c>
       <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
@@ -7097,15 +7085,15 @@
         <v>46273</v>
       </c>
       <c r="H179" t="n">
-        <v>47252</v>
+        <v>30791</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>15.35</v>
+        <v>42.67</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -7118,15 +7106,15 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>154593</v>
+        <v>152613</v>
       </c>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
@@ -7134,15 +7122,15 @@
         <v>46273</v>
       </c>
       <c r="H180" t="n">
-        <v>789603</v>
+        <v>30791</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SOFTYS BRASIL LTDA</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>13.38</v>
+        <v>106.83</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -7155,15 +7143,15 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>105228</v>
+        <v>136048</v>
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
@@ -7171,15 +7159,15 @@
         <v>46273</v>
       </c>
       <c r="H181" t="n">
-        <v>789423</v>
+        <v>30083</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>44.4</v>
+        <v>41.08</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -7200,7 +7188,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>134698</v>
+        <v>145832</v>
       </c>
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
@@ -7208,15 +7196,15 @@
         <v>46273</v>
       </c>
       <c r="H182" t="n">
-        <v>796414</v>
+        <v>30083</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J182" t="n">
-        <v>61.91</v>
+        <v>58.5</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
@@ -7229,15 +7217,15 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>139700</v>
+        <v>59935</v>
       </c>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
@@ -7245,15 +7233,15 @@
         <v>46273</v>
       </c>
       <c r="H183" t="n">
-        <v>796414</v>
+        <v>33286</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>32.68</v>
+        <v>36.59</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
@@ -7262,19 +7250,19 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>145</v>
+        <v>38</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>132982</v>
+        <v>97616</v>
       </c>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
@@ -7282,15 +7270,15 @@
         <v>46273</v>
       </c>
       <c r="H184" t="n">
-        <v>47252</v>
+        <v>33057</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>185.83</v>
+        <v>23.04</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -7299,19 +7287,19 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>163049</v>
+        <v>160027</v>
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
@@ -7319,15 +7307,15 @@
         <v>46273</v>
       </c>
       <c r="H185" t="n">
-        <v>30307</v>
+        <v>794671</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J185" t="n">
-        <v>189.96</v>
+        <v>37.65</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
@@ -7336,19 +7324,19 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>76180</v>
+        <v>18589</v>
       </c>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
@@ -7356,15 +7344,15 @@
         <v>46273</v>
       </c>
       <c r="H186" t="n">
-        <v>30791</v>
+        <v>789228</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>SANDOZ DO BRASI  IND. FARMAC LTDA (SP)</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>42.67</v>
+        <v>11.85</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
@@ -7373,56 +7361,62 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>139213</v>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
+        <v>21130</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>FKP07321</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="n">
+        <v>46478</v>
+      </c>
       <c r="G187" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H187" t="n">
-        <v>47252</v>
+        <v>789661</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>SANOFI MEDLEY FARMACEUTICA LTDA</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>127.11</v>
+        <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BERNARDO TEIXEIRA COSTA NETO</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>153154</v>
+        <v>154593</v>
       </c>
       <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
@@ -7430,15 +7424,15 @@
         <v>46273</v>
       </c>
       <c r="H188" t="n">
-        <v>5582</v>
+        <v>789603</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>SOFTYS BRASIL LTDA</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>54.33</v>
+        <v>13.38</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -7451,15 +7445,15 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>161224</v>
+        <v>113743</v>
       </c>
       <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
@@ -7467,15 +7461,15 @@
         <v>46273</v>
       </c>
       <c r="H189" t="n">
-        <v>47252</v>
+        <v>31267</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>17.75</v>
+        <v>7.87</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -7484,19 +7478,19 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>BERNARDO TEIXEIRA COSTA NETO</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>160027</v>
+        <v>160714</v>
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
@@ -7504,15 +7498,15 @@
         <v>46273</v>
       </c>
       <c r="H190" t="n">
-        <v>794671</v>
+        <v>31267</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>37.65</v>
+        <v>2855.24</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -7533,7 +7527,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>154573</v>
+        <v>139721</v>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
@@ -7541,15 +7535,15 @@
         <v>46273</v>
       </c>
       <c r="H191" t="n">
-        <v>47252</v>
+        <v>789525</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>53.35</v>
+        <v>118.72</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
@@ -7562,19 +7556,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">SUPERVISÃO HERTZ CE </t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>153194</v>
+        <v>154949</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>0000295575</t>
+          <t>2506277</t>
         </is>
       </c>
       <c r="F192" s="2" t="n">
@@ -7584,18 +7578,18 @@
         <v>46273</v>
       </c>
       <c r="H192" t="n">
-        <v>789423</v>
+        <v>789525</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J192" t="n">
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>315.09</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="193">
@@ -7638,19 +7632,19 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>160714</v>
+        <v>136617</v>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
@@ -7658,15 +7652,15 @@
         <v>46273</v>
       </c>
       <c r="H194" t="n">
-        <v>31267</v>
+        <v>30307</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>1047.42</v>
+        <v>166.74</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
@@ -7675,19 +7669,19 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>160714</v>
+        <v>132087</v>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
@@ -7695,15 +7689,15 @@
         <v>46273</v>
       </c>
       <c r="H195" t="n">
-        <v>31267</v>
+        <v>796414</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>1702.16</v>
+        <v>41.27</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -7716,15 +7710,15 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>55425</v>
+        <v>136905</v>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
@@ -7732,15 +7726,15 @@
         <v>46273</v>
       </c>
       <c r="H196" t="n">
-        <v>30791</v>
+        <v>796414</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>23.45</v>
+        <v>34.29</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
@@ -7749,19 +7743,19 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>52051</v>
+        <v>144156</v>
       </c>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
@@ -7769,15 +7763,15 @@
         <v>46273</v>
       </c>
       <c r="H197" t="n">
-        <v>793120</v>
+        <v>796414</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>322.68</v>
+        <v>54.4</v>
       </c>
       <c r="K197" t="n">
         <v>0</v>
@@ -7786,19 +7780,19 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>68659</v>
+        <v>158712</v>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
@@ -7806,15 +7800,15 @@
         <v>46273</v>
       </c>
       <c r="H198" t="n">
-        <v>47252</v>
+        <v>796414</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>76.8</v>
+        <v>32.68</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -7823,19 +7817,19 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>161961</v>
+        <v>155198</v>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
@@ -7843,15 +7837,15 @@
         <v>46273</v>
       </c>
       <c r="H199" t="n">
-        <v>30083</v>
+        <v>792141</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>47.1</v>
+        <v>239.37</v>
       </c>
       <c r="K199" t="n">
         <v>0</v>
@@ -7860,19 +7854,19 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>132087</v>
+        <v>157689</v>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
@@ -7880,15 +7874,15 @@
         <v>46273</v>
       </c>
       <c r="H200" t="n">
-        <v>796414</v>
+        <v>792141</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>41.27</v>
+        <v>163.4</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -7897,19 +7891,19 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>153702</v>
+        <v>161317</v>
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
@@ -7917,15 +7911,15 @@
         <v>46273</v>
       </c>
       <c r="H201" t="n">
-        <v>47252</v>
+        <v>796383</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>3.2</v>
+        <v>16.69</v>
       </c>
       <c r="K201" t="n">
         <v>0</v>
@@ -7938,15 +7932,15 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>136905</v>
+        <v>6181</v>
       </c>
       <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
@@ -7954,15 +7948,15 @@
         <v>46273</v>
       </c>
       <c r="H202" t="n">
-        <v>796414</v>
+        <v>47252</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J202" t="n">
-        <v>34.29</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -7971,19 +7965,19 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>141631</v>
+        <v>10448</v>
       </c>
       <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
@@ -7991,15 +7985,15 @@
         <v>46273</v>
       </c>
       <c r="H203" t="n">
-        <v>30083</v>
+        <v>47252</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>23.89</v>
+        <v>7.37</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -8008,19 +8002,19 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>50</v>
+        <v>145</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>88366</v>
+        <v>17310</v>
       </c>
       <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
@@ -8036,7 +8030,7 @@
         </is>
       </c>
       <c r="J204" t="n">
-        <v>55.68</v>
+        <v>25.97</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -8057,7 +8051,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>157673</v>
+        <v>68659</v>
       </c>
       <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
@@ -8073,7 +8067,7 @@
         </is>
       </c>
       <c r="J205" t="n">
-        <v>16.68</v>
+        <v>76.8</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -8082,19 +8076,19 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>136617</v>
+        <v>69280</v>
       </c>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr"/>
@@ -8102,15 +8096,15 @@
         <v>46273</v>
       </c>
       <c r="H206" t="n">
-        <v>30307</v>
+        <v>47252</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>166.74</v>
+        <v>232.82</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -8119,19 +8113,19 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>6181</v>
+        <v>85707</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
@@ -8147,7 +8141,7 @@
         </is>
       </c>
       <c r="J207" t="n">
-        <v>68.65000000000001</v>
+        <v>273.57</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -8156,19 +8150,19 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>JONATHAS SANTOS ANDRADE - FARMA</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>144156</v>
+        <v>88366</v>
       </c>
       <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
@@ -8176,15 +8170,15 @@
         <v>46273</v>
       </c>
       <c r="H208" t="n">
-        <v>796414</v>
+        <v>47252</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>54.4</v>
+        <v>55.68</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -8193,19 +8187,19 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>146565</v>
+        <v>110248</v>
       </c>
       <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
@@ -8213,15 +8207,15 @@
         <v>46273</v>
       </c>
       <c r="H209" t="n">
-        <v>30083</v>
+        <v>47252</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>5.99</v>
+        <v>2.31</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -8242,7 +8236,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>85707</v>
+        <v>140234</v>
       </c>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr"/>
@@ -8258,7 +8252,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>273.57</v>
+        <v>7.84</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -8271,15 +8265,15 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>157689</v>
+        <v>141092</v>
       </c>
       <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr"/>
@@ -8287,15 +8281,15 @@
         <v>46273</v>
       </c>
       <c r="H211" t="n">
-        <v>792141</v>
+        <v>47252</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J211" t="n">
-        <v>163.4</v>
+        <v>7.72</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -8316,7 +8310,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>141092</v>
+        <v>153702</v>
       </c>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
@@ -8332,7 +8326,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>7.72</v>
+        <v>3.2</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -8341,19 +8335,19 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>154929</v>
+        <v>157673</v>
       </c>
       <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
@@ -8361,15 +8355,15 @@
         <v>46273</v>
       </c>
       <c r="H213" t="n">
-        <v>794365</v>
+        <v>47252</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J213" t="n">
-        <v>58.8</v>
+        <v>16.68</v>
       </c>
       <c r="K213" t="n">
         <v>0</v>
@@ -8382,15 +8376,15 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>140234</v>
+        <v>52051</v>
       </c>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
@@ -8398,7 +8392,7 @@
         <v>46273</v>
       </c>
       <c r="H214" t="n">
-        <v>47252</v>
+        <v>793120</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -8406,7 +8400,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>7.84</v>
+        <v>322.68</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -8419,34 +8413,40 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t xml:space="preserve">SUPERVISÃO HERTZ CE </t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>17310</v>
-      </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
+        <v>153194</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>0000295575</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="n">
+        <v>46539</v>
+      </c>
       <c r="G215" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H215" t="n">
-        <v>47252</v>
+        <v>789423</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J215" t="n">
-        <v>25.97</v>
+        <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>0</v>
+        <v>315.09</v>
       </c>
     </row>
     <row r="216">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>146088</v>
+        <v>154929</v>
       </c>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
@@ -8472,15 +8472,15 @@
         <v>46273</v>
       </c>
       <c r="H216" t="n">
-        <v>33286</v>
+        <v>794365</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J216" t="n">
-        <v>8.07</v>
+        <v>58.8</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -8493,15 +8493,15 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>158712</v>
+        <v>55425</v>
       </c>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
@@ -8509,15 +8509,15 @@
         <v>46273</v>
       </c>
       <c r="H217" t="n">
-        <v>796414</v>
+        <v>30791</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J217" t="n">
-        <v>32.68</v>
+        <v>23.45</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -8526,19 +8526,19 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>155198</v>
+        <v>141631</v>
       </c>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr"/>
@@ -8546,15 +8546,15 @@
         <v>46273</v>
       </c>
       <c r="H218" t="n">
-        <v>792141</v>
+        <v>30083</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J218" t="n">
-        <v>239.37</v>
+        <v>23.89</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -8563,19 +8563,19 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>PAULO CESAR DAMACENA LEMOS - HB</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>10448</v>
+        <v>146565</v>
       </c>
       <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr"/>
@@ -8583,15 +8583,15 @@
         <v>46273</v>
       </c>
       <c r="H219" t="n">
-        <v>47252</v>
+        <v>30083</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J219" t="n">
-        <v>7.37</v>
+        <v>5.99</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -8600,19 +8600,19 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>110248</v>
+        <v>161961</v>
       </c>
       <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr"/>
@@ -8620,15 +8620,15 @@
         <v>46273</v>
       </c>
       <c r="H220" t="n">
-        <v>47252</v>
+        <v>30083</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J220" t="n">
-        <v>2.31</v>
+        <v>47.1</v>
       </c>
       <c r="K220" t="n">
         <v>0</v>
@@ -8637,19 +8637,19 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>69280</v>
+        <v>146088</v>
       </c>
       <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr"/>
@@ -8657,15 +8657,15 @@
         <v>46273</v>
       </c>
       <c r="H221" t="n">
-        <v>47252</v>
+        <v>33286</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
         </is>
       </c>
       <c r="J221" t="n">
-        <v>232.82</v>
+        <v>8.07</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -8674,19 +8674,19 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>161317</v>
+        <v>155645</v>
       </c>
       <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr"/>
@@ -8694,15 +8694,15 @@
         <v>46273</v>
       </c>
       <c r="H222" t="n">
-        <v>796383</v>
+        <v>794671</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J222" t="n">
-        <v>16.69</v>
+        <v>164.64</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -8715,144 +8715,126 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>54836</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>0942620</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="n">
-        <v>46539</v>
-      </c>
+        <v>160714</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
       <c r="G223" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H223" t="n">
-        <v>30791</v>
+        <v>31267</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J223" t="n">
-        <v>0</v>
+        <v>1047.42</v>
       </c>
       <c r="K223" t="n">
-        <v>27.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>147083</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>571473</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="n">
-        <v>46478</v>
-      </c>
+        <v>160714</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H224" t="n">
-        <v>47252</v>
+        <v>31267</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
         </is>
       </c>
       <c r="J224" t="n">
-        <v>0</v>
+        <v>1702.16</v>
       </c>
       <c r="K224" t="n">
-        <v>40.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>19216</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>B25E1660</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="n">
-        <v>46508</v>
-      </c>
+        <v>162978</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H225" t="n">
-        <v>47252</v>
+        <v>793527</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>AGAPLASTIC INDUSTRIA E COMERCIO LTDA - AGPMED</t>
         </is>
       </c>
       <c r="J225" t="n">
-        <v>0</v>
+        <v>31.57</v>
       </c>
       <c r="K225" t="n">
-        <v>8.210000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>162978</v>
+        <v>136632</v>
       </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr"/>
@@ -8860,15 +8842,15 @@
         <v>46273</v>
       </c>
       <c r="H226" t="n">
-        <v>793527</v>
+        <v>30307</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>AGAPLASTIC INDUSTRIA E COMERCIO LTDA - AGPMED</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J226" t="n">
-        <v>31.57</v>
+        <v>166.74</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -8877,19 +8859,19 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>154970</v>
+        <v>140514</v>
       </c>
       <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr"/>
@@ -8897,15 +8879,15 @@
         <v>46273</v>
       </c>
       <c r="H227" t="n">
-        <v>794365</v>
+        <v>30307</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J227" t="n">
-        <v>29.87</v>
+        <v>166.74</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -8914,19 +8896,19 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>118001</v>
+        <v>157509</v>
       </c>
       <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr"/>
@@ -8934,15 +8916,15 @@
         <v>46273</v>
       </c>
       <c r="H228" t="n">
-        <v>790808</v>
+        <v>30307</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J228" t="n">
-        <v>19.9</v>
+        <v>139.96</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -8951,19 +8933,19 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>129962</v>
+        <v>139633</v>
       </c>
       <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr"/>
@@ -8971,15 +8953,15 @@
         <v>46273</v>
       </c>
       <c r="H229" t="n">
-        <v>47252</v>
+        <v>75647</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>CREMER S/A</t>
         </is>
       </c>
       <c r="J229" t="n">
-        <v>56.84</v>
+        <v>66.56</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -9000,7 +8982,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>157923</v>
+        <v>139701</v>
       </c>
       <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr"/>
@@ -9008,15 +8990,15 @@
         <v>46273</v>
       </c>
       <c r="H230" t="n">
-        <v>73474</v>
+        <v>796414</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>SANFARMA INDUSTRIA, COMERCIO E IMPORTACAO E EXPORTACAO LTDA</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J230" t="n">
-        <v>44.61</v>
+        <v>38.28</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -9025,38 +9007,44 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>141729</v>
-      </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
+        <v>19216</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>B25E1660</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="n">
+        <v>46508</v>
+      </c>
       <c r="G231" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H231" t="n">
-        <v>30791</v>
+        <v>47252</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J231" t="n">
-        <v>34.04</v>
+        <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>0</v>
+        <v>8.210000000000001</v>
       </c>
     </row>
     <row r="232">
@@ -9074,7 +9062,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>142180</v>
+        <v>69248</v>
       </c>
       <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr"/>
@@ -9090,7 +9078,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>72.52</v>
+        <v>126.58</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -9099,19 +9087,19 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>160175</v>
+        <v>129962</v>
       </c>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr"/>
@@ -9119,15 +9107,15 @@
         <v>46273</v>
       </c>
       <c r="H233" t="n">
-        <v>789204</v>
+        <v>47252</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>MEDIX BRASIL PROD HOSPIT E ODONTOLOGICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J233" t="n">
-        <v>36.79</v>
+        <v>56.84</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -9140,15 +9128,15 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>148120</v>
+        <v>139541</v>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr"/>
@@ -9156,15 +9144,15 @@
         <v>46273</v>
       </c>
       <c r="H234" t="n">
-        <v>790808</v>
+        <v>47252</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J234" t="n">
-        <v>11.54</v>
+        <v>7.38</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
@@ -9173,19 +9161,19 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>124036</v>
+        <v>142180</v>
       </c>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr"/>
@@ -9193,15 +9181,15 @@
         <v>46273</v>
       </c>
       <c r="H235" t="n">
-        <v>30791</v>
+        <v>47252</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J235" t="n">
-        <v>68.64</v>
+        <v>72.52</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -9210,38 +9198,44 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>139701</v>
-      </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
+        <v>147083</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>571473</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="n">
+        <v>46478</v>
+      </c>
       <c r="G236" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H236" t="n">
-        <v>796414</v>
+        <v>47252</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J236" t="n">
-        <v>38.28</v>
+        <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>0</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="237">
@@ -9251,15 +9245,15 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>139633</v>
+        <v>151754</v>
       </c>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr"/>
@@ -9267,15 +9261,15 @@
         <v>46273</v>
       </c>
       <c r="H237" t="n">
-        <v>75647</v>
+        <v>789423</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>CREMER S/A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J237" t="n">
-        <v>66.56</v>
+        <v>110.28</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -9296,7 +9290,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>151754</v>
+        <v>74349</v>
       </c>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr"/>
@@ -9304,15 +9298,15 @@
         <v>46273</v>
       </c>
       <c r="H238" t="n">
-        <v>789423</v>
+        <v>794365</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J238" t="n">
-        <v>110.28</v>
+        <v>16.14</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -9333,7 +9327,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>141514</v>
+        <v>154970</v>
       </c>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr"/>
@@ -9341,15 +9335,15 @@
         <v>46273</v>
       </c>
       <c r="H239" t="n">
-        <v>33057</v>
+        <v>794365</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>NATULAB LABORATORIO LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J239" t="n">
-        <v>14.97</v>
+        <v>29.87</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -9358,56 +9352,62 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>140514</v>
-      </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
+        <v>54836</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>0942620</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="n">
+        <v>46539</v>
+      </c>
       <c r="G240" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="H240" t="n">
-        <v>30307</v>
+        <v>30791</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J240" t="n">
-        <v>166.74</v>
+        <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>136632</v>
+        <v>124036</v>
       </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr"/>
@@ -9415,15 +9415,15 @@
         <v>46273</v>
       </c>
       <c r="H241" t="n">
-        <v>30307</v>
+        <v>30791</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J241" t="n">
-        <v>166.74</v>
+        <v>68.64</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>74349</v>
+        <v>141729</v>
       </c>
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr"/>
@@ -9452,15 +9452,15 @@
         <v>46273</v>
       </c>
       <c r="H242" t="n">
-        <v>794365</v>
+        <v>30791</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J242" t="n">
-        <v>16.14</v>
+        <v>34.04</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -9473,15 +9473,15 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>147223</v>
+        <v>142080</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr"/>
@@ -9489,15 +9489,15 @@
         <v>46273</v>
       </c>
       <c r="H243" t="n">
-        <v>33057</v>
+        <v>30083</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>NATULAB LABORATORIO LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J243" t="n">
-        <v>100.29</v>
+        <v>41.99</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -9510,15 +9510,15 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>142080</v>
+        <v>118001</v>
       </c>
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr"/>
@@ -9526,15 +9526,15 @@
         <v>46273</v>
       </c>
       <c r="H244" t="n">
-        <v>30083</v>
+        <v>790808</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
         </is>
       </c>
       <c r="J244" t="n">
-        <v>41.99</v>
+        <v>19.9</v>
       </c>
       <c r="K244" t="n">
         <v>0</v>
@@ -9547,15 +9547,15 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>69248</v>
+        <v>148120</v>
       </c>
       <c r="E245" t="inlineStr"/>
       <c r="F245" t="inlineStr"/>
@@ -9563,15 +9563,15 @@
         <v>46273</v>
       </c>
       <c r="H245" t="n">
-        <v>47252</v>
+        <v>790808</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (NVQ)</t>
         </is>
       </c>
       <c r="J245" t="n">
-        <v>126.58</v>
+        <v>11.54</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -9580,19 +9580,19 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>MARIA ELIZIANE MACIEL DE SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>157509</v>
+        <v>141514</v>
       </c>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr"/>
@@ -9600,15 +9600,15 @@
         <v>46273</v>
       </c>
       <c r="H246" t="n">
-        <v>30307</v>
+        <v>33057</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J246" t="n">
-        <v>139.96</v>
+        <v>14.97</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -9617,19 +9617,19 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>139541</v>
+        <v>147223</v>
       </c>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr"/>
@@ -9637,17 +9637,91 @@
         <v>46273</v>
       </c>
       <c r="H247" t="n">
-        <v>47252</v>
+        <v>33057</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J247" t="n">
-        <v>7.38</v>
+        <v>100.29</v>
       </c>
       <c r="K247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>69</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>157923</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H248" t="n">
+        <v>73474</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>SANFARMA INDUSTRIA, COMERCIO E IMPORTACAO E EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="J248" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>39</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>160175</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="H249" t="n">
+        <v>789204</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>MEDIX BRASIL PROD HOSPIT E ODONTOLOGICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J249" t="n">
+        <v>36.79</v>
+      </c>
+      <c r="K249" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/vadas.xlsx
+++ b/data/vadas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,15 +496,15 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>160026</v>
+        <v>136630</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -512,15 +512,15 @@
         <v>46274</v>
       </c>
       <c r="H2" t="n">
-        <v>794671</v>
+        <v>30307</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>39.26</v>
+        <v>1233.36</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -529,19 +529,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>161253</v>
+        <v>140629</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -549,15 +549,15 @@
         <v>46274</v>
       </c>
       <c r="H3" t="n">
-        <v>795345</v>
+        <v>30307</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17.18</v>
+        <v>95.92</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -566,19 +566,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>105180</v>
+        <v>152311</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -586,15 +586,15 @@
         <v>46274</v>
       </c>
       <c r="H4" t="n">
-        <v>33928</v>
+        <v>30307</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>69.93000000000001</v>
+        <v>522.64</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>161407</v>
+        <v>157510</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -623,15 +623,15 @@
         <v>46274</v>
       </c>
       <c r="H5" t="n">
-        <v>794365</v>
+        <v>30307</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>24.26</v>
+        <v>1276</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -640,19 +640,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>154945</v>
+        <v>163047</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -660,15 +660,15 @@
         <v>46274</v>
       </c>
       <c r="H6" t="n">
-        <v>794365</v>
+        <v>30307</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>69.18000000000001</v>
+        <v>859.64</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -677,19 +677,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>161744</v>
+        <v>161253</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -697,15 +697,15 @@
         <v>46274</v>
       </c>
       <c r="H7" t="n">
-        <v>794319</v>
+        <v>795345</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>503.19</v>
+        <v>17.18</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -714,19 +714,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>155661</v>
+        <v>158354</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -734,15 +734,15 @@
         <v>46274</v>
       </c>
       <c r="H8" t="n">
-        <v>794671</v>
+        <v>139553</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>40.27</v>
+        <v>188.12</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -751,19 +751,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>156161</v>
+        <v>153947</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>648.98</v>
+        <v>260.32</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>158354</v>
+        <v>156161</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -808,15 +808,15 @@
         <v>46274</v>
       </c>
       <c r="H10" t="n">
-        <v>139553</v>
+        <v>794319</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>188.12</v>
+        <v>648.98</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -825,19 +825,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>152311</v>
+        <v>156163</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -845,15 +845,15 @@
         <v>46274</v>
       </c>
       <c r="H11" t="n">
-        <v>30307</v>
+        <v>794319</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>522.64</v>
+        <v>71.94</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>163047</v>
+        <v>161744</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -882,15 +882,15 @@
         <v>46274</v>
       </c>
       <c r="H12" t="n">
-        <v>30307</v>
+        <v>794319</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>859.64</v>
+        <v>503.19</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -899,19 +899,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>157510</v>
+        <v>105180</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -919,15 +919,15 @@
         <v>46274</v>
       </c>
       <c r="H13" t="n">
-        <v>30307</v>
+        <v>33928</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1020.8</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -936,19 +936,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>139894</v>
+        <v>82678</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -956,15 +956,15 @@
         <v>46274</v>
       </c>
       <c r="H14" t="n">
-        <v>789525</v>
+        <v>47252</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>26.7</v>
+        <v>21.39</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -973,19 +973,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>136630</v>
+        <v>154945</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -993,15 +993,15 @@
         <v>46274</v>
       </c>
       <c r="H15" t="n">
-        <v>30307</v>
+        <v>794365</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1233.36</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1010,19 +1010,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>153948</v>
+        <v>161407</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1030,15 +1030,15 @@
         <v>46274</v>
       </c>
       <c r="H16" t="n">
-        <v>794319</v>
+        <v>794365</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>927.5</v>
+        <v>24.26</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>158356</v>
+        <v>161804</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -1067,15 +1067,15 @@
         <v>46274</v>
       </c>
       <c r="H17" t="n">
-        <v>139553</v>
+        <v>796496</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>MAXI CONFORT IMPORTACAO E EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1308.39</v>
+        <v>341.34</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1084,19 +1084,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>158382</v>
+        <v>138992</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -1104,15 +1104,15 @@
         <v>46274</v>
       </c>
       <c r="H18" t="n">
-        <v>139553</v>
+        <v>791717</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>339.48</v>
+        <v>28.98</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1121,19 +1121,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>158384</v>
+        <v>138993</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1141,15 +1141,15 @@
         <v>46274</v>
       </c>
       <c r="H19" t="n">
-        <v>139553</v>
+        <v>791717</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>444.52</v>
+        <v>28.98</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1158,19 +1158,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>158566</v>
+        <v>118990</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1178,15 +1178,15 @@
         <v>46274</v>
       </c>
       <c r="H20" t="n">
-        <v>794671</v>
+        <v>33057</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>51.65</v>
+        <v>116.23</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1195,19 +1195,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>158383</v>
+        <v>155661</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1215,15 +1215,15 @@
         <v>46274</v>
       </c>
       <c r="H21" t="n">
-        <v>139553</v>
+        <v>794671</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>113.16</v>
+        <v>40.27</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1232,19 +1232,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>145830</v>
+        <v>160026</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -1252,15 +1252,15 @@
         <v>46274</v>
       </c>
       <c r="H22" t="n">
-        <v>30083</v>
+        <v>794671</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>18.59</v>
+        <v>39.26</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1269,19 +1269,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>156160</v>
+        <v>139894</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1289,15 +1289,15 @@
         <v>46274</v>
       </c>
       <c r="H23" t="n">
-        <v>794319</v>
+        <v>789525</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>259.59</v>
+        <v>26.7</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1306,19 +1306,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>136623</v>
+        <v>19054</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1326,15 +1326,15 @@
         <v>46274</v>
       </c>
       <c r="H24" t="n">
-        <v>30307</v>
+        <v>2378</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>BELFAR LTDA</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>183.84</v>
+        <v>6.47</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1343,19 +1343,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>134701</v>
+        <v>136623</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1363,15 +1363,15 @@
         <v>46274</v>
       </c>
       <c r="H25" t="n">
-        <v>789423</v>
+        <v>30307</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>23.3</v>
+        <v>183.84</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1380,19 +1380,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>163048</v>
+        <v>136630</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1203.5</v>
+        <v>205.56</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1417,19 +1417,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>156187</v>
+        <v>157509</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -1437,15 +1437,15 @@
         <v>46274</v>
       </c>
       <c r="H27" t="n">
-        <v>794365</v>
+        <v>30307</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>77.83</v>
+        <v>259.97</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1454,19 +1454,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>157509</v>
+        <v>163048</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>119.96</v>
+        <v>1203.5</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1491,19 +1491,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>139215</v>
+        <v>156646</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -1511,15 +1511,15 @@
         <v>46274</v>
       </c>
       <c r="H29" t="n">
-        <v>793056</v>
+        <v>795345</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>14142.51</v>
+        <v>27.3</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1532,15 +1532,15 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27723</v>
+        <v>158356</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1548,15 +1548,15 @@
         <v>46274</v>
       </c>
       <c r="H30" t="n">
-        <v>789423</v>
+        <v>139553</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>28.19</v>
+        <v>1308.39</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1569,15 +1569,15 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>162451</v>
+        <v>158382</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1585,15 +1585,15 @@
         <v>46274</v>
       </c>
       <c r="H31" t="n">
-        <v>789423</v>
+        <v>139553</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>339.48</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1602,19 +1602,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>136634</v>
+        <v>158383</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1622,15 +1622,15 @@
         <v>46274</v>
       </c>
       <c r="H32" t="n">
-        <v>30307</v>
+        <v>139553</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>616.6799999999999</v>
+        <v>113.16</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1643,15 +1643,15 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>74713</v>
+        <v>158384</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -1659,15 +1659,15 @@
         <v>46274</v>
       </c>
       <c r="H33" t="n">
-        <v>789525</v>
+        <v>139553</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>58.13</v>
+        <v>444.52</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1676,19 +1676,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>158363</v>
+        <v>153308</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1696,15 +1696,15 @@
         <v>46274</v>
       </c>
       <c r="H34" t="n">
-        <v>139553</v>
+        <v>794319</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1308.39</v>
+        <v>101.22</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1713,19 +1713,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>139738</v>
+        <v>153948</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -1733,15 +1733,15 @@
         <v>46274</v>
       </c>
       <c r="H35" t="n">
-        <v>789525</v>
+        <v>794319</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>87.69</v>
+        <v>927.5</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1750,19 +1750,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>154932</v>
+        <v>156160</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1770,15 +1770,15 @@
         <v>46274</v>
       </c>
       <c r="H36" t="n">
-        <v>789525</v>
+        <v>794319</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>13.31</v>
+        <v>259.59</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1787,19 +1787,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>161408</v>
+        <v>161314</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1807,15 +1807,15 @@
         <v>46274</v>
       </c>
       <c r="H37" t="n">
-        <v>794365</v>
+        <v>796383</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>40.01</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>153947</v>
+        <v>134701</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1844,15 +1844,15 @@
         <v>46274</v>
       </c>
       <c r="H38" t="n">
-        <v>794319</v>
+        <v>789423</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1192.5</v>
+        <v>23.3</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1861,19 +1861,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>74535</v>
+        <v>145830</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -1881,15 +1881,15 @@
         <v>46274</v>
       </c>
       <c r="H39" t="n">
-        <v>789525</v>
+        <v>30083</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>44.87</v>
+        <v>18.59</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1902,15 +1902,15 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>137009</v>
+        <v>130133</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1918,15 +1918,15 @@
         <v>46274</v>
       </c>
       <c r="H40" t="n">
-        <v>30307</v>
+        <v>791717</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>822.24</v>
+        <v>19.58</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -1935,19 +1935,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>139826</v>
+        <v>158566</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -1955,15 +1955,15 @@
         <v>46274</v>
       </c>
       <c r="H41" t="n">
-        <v>30083</v>
+        <v>794671</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>18.59</v>
+        <v>51.65</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -1972,19 +1972,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>74616</v>
+        <v>136634</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -1992,15 +1992,15 @@
         <v>46274</v>
       </c>
       <c r="H42" t="n">
-        <v>789525</v>
+        <v>30307</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>123.78</v>
+        <v>616.6799999999999</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2009,19 +2009,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>139929</v>
+        <v>157509</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -2029,15 +2029,15 @@
         <v>46274</v>
       </c>
       <c r="H43" t="n">
-        <v>789525</v>
+        <v>30307</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>41.5</v>
+        <v>119.96</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2046,19 +2046,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>158352</v>
+        <v>161254</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -2066,15 +2066,15 @@
         <v>46274</v>
       </c>
       <c r="H44" t="n">
-        <v>139553</v>
+        <v>795345</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>188.12</v>
+        <v>40.5</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2083,19 +2083,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>158385</v>
+        <v>155035</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -2103,15 +2103,15 @@
         <v>46274</v>
       </c>
       <c r="H45" t="n">
-        <v>139553</v>
+        <v>792141</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>666.78</v>
+        <v>221.66</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2124,15 +2124,15 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>158351</v>
+        <v>27723</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -2140,15 +2140,15 @@
         <v>46274</v>
       </c>
       <c r="H46" t="n">
-        <v>139553</v>
+        <v>789423</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>376.24</v>
+        <v>28.19</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2157,19 +2157,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>139951</v>
+        <v>162451</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -2177,15 +2177,15 @@
         <v>46274</v>
       </c>
       <c r="H47" t="n">
-        <v>789525</v>
+        <v>789423</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>55.41</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2194,19 +2194,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>156160</v>
+        <v>156187</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -2214,15 +2214,15 @@
         <v>46274</v>
       </c>
       <c r="H48" t="n">
-        <v>794319</v>
+        <v>794365</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1038.37</v>
+        <v>77.83</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2231,19 +2231,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>143167</v>
+        <v>139826</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2251,15 +2251,15 @@
         <v>46274</v>
       </c>
       <c r="H49" t="n">
-        <v>30791</v>
+        <v>30083</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>37.51</v>
+        <v>36.18</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>160521</v>
+        <v>144874</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -2288,15 +2288,15 @@
         <v>46274</v>
       </c>
       <c r="H50" t="n">
-        <v>794671</v>
+        <v>30083</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>32.93</v>
+        <v>14.99</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2305,19 +2305,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>139737</v>
+        <v>148254</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -2325,15 +2325,15 @@
         <v>46274</v>
       </c>
       <c r="H51" t="n">
-        <v>794365</v>
+        <v>789112</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>MILI SA</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>82</v>
+        <v>152.91</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2342,19 +2342,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>139926</v>
+        <v>139215</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -2362,15 +2362,15 @@
         <v>46274</v>
       </c>
       <c r="H52" t="n">
-        <v>789525</v>
+        <v>793056</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>72.63</v>
+        <v>14142.51</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2379,19 +2379,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>146414</v>
+        <v>160129</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
@@ -2399,15 +2399,15 @@
         <v>46274</v>
       </c>
       <c r="H53" t="n">
-        <v>33286</v>
+        <v>795898</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+          <t>VIDA FORTE NUTRIENTES INDUSTRIA E COMERCIO DE PRODUTOS NATUR</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>33.97</v>
+        <v>264.68</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2416,19 +2416,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>159933</v>
+        <v>137009</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
@@ -2436,15 +2436,15 @@
         <v>46274</v>
       </c>
       <c r="H54" t="n">
-        <v>789525</v>
+        <v>30307</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>30</v>
+        <v>822.24</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2453,19 +2453,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>140278</v>
+        <v>156643</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -2473,15 +2473,15 @@
         <v>46274</v>
       </c>
       <c r="H55" t="n">
-        <v>793056</v>
+        <v>795345</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>4562.85</v>
+        <v>23.7</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2490,19 +2490,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>47198</v>
+        <v>158352</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -2510,15 +2510,15 @@
         <v>46274</v>
       </c>
       <c r="H56" t="n">
-        <v>31305</v>
+        <v>139553</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LABORATORIO GLOBO LTDA</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>152.47</v>
+        <v>188.12</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2531,15 +2531,15 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>162755</v>
+        <v>158363</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -2547,15 +2547,15 @@
         <v>46274</v>
       </c>
       <c r="H57" t="n">
-        <v>5582</v>
+        <v>139553</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>27.9</v>
+        <v>1308.39</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2564,19 +2564,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>156003</v>
+        <v>153947</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
@@ -2584,15 +2584,15 @@
         <v>46274</v>
       </c>
       <c r="H58" t="n">
-        <v>794365</v>
+        <v>794319</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>92.09</v>
+        <v>1192.5</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2601,19 +2601,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>160535</v>
+        <v>92525</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -2621,15 +2621,15 @@
         <v>46274</v>
       </c>
       <c r="H59" t="n">
-        <v>789525</v>
+        <v>47252</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>49.39</v>
+        <v>29.21</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2638,19 +2638,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>163049</v>
+        <v>161408</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -2658,15 +2658,15 @@
         <v>46274</v>
       </c>
       <c r="H60" t="n">
-        <v>30307</v>
+        <v>794365</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1203.5</v>
+        <v>40.01</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2675,19 +2675,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>156004</v>
+        <v>139826</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
@@ -2695,15 +2695,15 @@
         <v>46274</v>
       </c>
       <c r="H61" t="n">
-        <v>794365</v>
+        <v>30083</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>137.93</v>
+        <v>18.59</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2712,19 +2712,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>161743</v>
+        <v>140453</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -2732,15 +2732,15 @@
         <v>46274</v>
       </c>
       <c r="H62" t="n">
-        <v>794319</v>
+        <v>30083</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>167.73</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2753,15 +2753,15 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>136622</v>
+        <v>141132</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
@@ -2769,15 +2769,15 @@
         <v>46274</v>
       </c>
       <c r="H63" t="n">
-        <v>30307</v>
+        <v>789112</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>MILI SA</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>183.84</v>
+        <v>260.91</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2786,19 +2786,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>160813</v>
+        <v>162363</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -2806,15 +2806,15 @@
         <v>46274</v>
       </c>
       <c r="H64" t="n">
-        <v>789423</v>
+        <v>791717</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>32.82</v>
+        <v>18.78</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2823,19 +2823,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>160714</v>
+        <v>144229</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
@@ -2843,15 +2843,15 @@
         <v>46274</v>
       </c>
       <c r="H65" t="n">
-        <v>31267</v>
+        <v>789603</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>SOFTYS BRASIL LTDA</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>283.09</v>
+        <v>206.94</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2860,19 +2860,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>161940</v>
+        <v>74535</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
@@ -2880,15 +2880,15 @@
         <v>46274</v>
       </c>
       <c r="H66" t="n">
-        <v>789603</v>
+        <v>789525</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOFTYS BRASIL LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>116.64</v>
+        <v>44.87</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -2897,19 +2897,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>153947</v>
+        <v>74616</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
@@ -2917,15 +2917,15 @@
         <v>46274</v>
       </c>
       <c r="H67" t="n">
-        <v>794319</v>
+        <v>789525</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>530</v>
+        <v>123.78</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -2934,19 +2934,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>84018</v>
+        <v>74713</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
@@ -2954,15 +2954,15 @@
         <v>46274</v>
       </c>
       <c r="H68" t="n">
-        <v>33928</v>
+        <v>789525</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>52.4</v>
+        <v>58.13</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>139919</v>
+        <v>139738</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
@@ -2991,15 +2991,15 @@
         <v>46274</v>
       </c>
       <c r="H69" t="n">
-        <v>794365</v>
+        <v>789525</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>14.89</v>
+        <v>87.69</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3008,19 +3008,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>158379</v>
+        <v>139929</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
@@ -3028,15 +3028,15 @@
         <v>46274</v>
       </c>
       <c r="H70" t="n">
-        <v>139553</v>
+        <v>789525</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>113.16</v>
+        <v>41.5</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3045,19 +3045,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>136624</v>
+        <v>154932</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
@@ -3065,15 +3065,15 @@
         <v>46274</v>
       </c>
       <c r="H71" t="n">
-        <v>30307</v>
+        <v>789525</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>183.84</v>
+        <v>13.31</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>140745</v>
+        <v>136633</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -3102,15 +3102,15 @@
         <v>46274</v>
       </c>
       <c r="H72" t="n">
-        <v>789423</v>
+        <v>30307</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>20.01</v>
+        <v>330</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>163046</v>
+        <v>157510</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>859.64</v>
+        <v>389.95</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>158387</v>
+        <v>158351</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>135.44</v>
+        <v>376.24</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3193,19 +3193,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>154952</v>
+        <v>158385</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -3213,15 +3213,15 @@
         <v>46274</v>
       </c>
       <c r="H75" t="n">
-        <v>789525</v>
+        <v>139553</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>14.8</v>
+        <v>2310.65</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3230,19 +3230,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>86690</v>
+        <v>156160</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
@@ -3250,15 +3250,15 @@
         <v>46274</v>
       </c>
       <c r="H76" t="n">
-        <v>793186</v>
+        <v>794319</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ACCUMED PRODUTOS MEDICO HOSPITALARES LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>215.96</v>
+        <v>1038.37</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3267,19 +3267,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>163433</v>
+        <v>58920</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
@@ -3287,15 +3287,15 @@
         <v>46274</v>
       </c>
       <c r="H77" t="n">
-        <v>794671</v>
+        <v>793261</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>FARMAX DISTRIBUIDORA S.A</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>91.18000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3304,19 +3304,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>160534</v>
+        <v>149193</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
@@ -3324,15 +3324,15 @@
         <v>46274</v>
       </c>
       <c r="H78" t="n">
-        <v>789525</v>
+        <v>793261</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>FARMAX DISTRIBUIDORA S.A</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>31.83</v>
+        <v>10.05</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>155645</v>
+        <v>155198</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
@@ -3361,15 +3361,15 @@
         <v>46274</v>
       </c>
       <c r="H79" t="n">
-        <v>794671</v>
+        <v>792141</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>41.16</v>
+        <v>366.49</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3378,19 +3378,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>156162</v>
+        <v>157689</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
@@ -3398,15 +3398,15 @@
         <v>46274</v>
       </c>
       <c r="H80" t="n">
-        <v>794319</v>
+        <v>792141</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>199.92</v>
+        <v>196.08</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3415,19 +3415,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>156161</v>
+        <v>79243</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
@@ -3435,15 +3435,15 @@
         <v>46274</v>
       </c>
       <c r="H81" t="n">
-        <v>794319</v>
+        <v>47252</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>129.8</v>
+        <v>11.47</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3452,19 +3452,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>105538</v>
+        <v>139737</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
@@ -3472,15 +3472,15 @@
         <v>46274</v>
       </c>
       <c r="H82" t="n">
-        <v>789423</v>
+        <v>794365</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>28.44</v>
+        <v>82</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3489,19 +3489,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>152312</v>
+        <v>143167</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
@@ -3509,15 +3509,15 @@
         <v>46274</v>
       </c>
       <c r="H83" t="n">
-        <v>30307</v>
+        <v>30791</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>348.43</v>
+        <v>37.51</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3526,19 +3526,19 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>106</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>157509</v>
+        <v>146414</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
@@ -3546,17 +3546,1793 @@
         <v>46274</v>
       </c>
       <c r="H84" t="n">
+        <v>33286</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>46</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>160521</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H85" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>120</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>139926</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H86" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>120</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>139951</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H87" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>120</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>159933</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H88" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>30</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>136622</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H89" t="n">
         <v>30307</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
-      <c r="J84" t="n">
+      <c r="J89" t="n">
+        <v>183.84</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>69</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>163049</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H90" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>1203.5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>46</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>161249</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H91" t="n">
+        <v>795345</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>46</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>161256</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H92" t="n">
+        <v>795345</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>39</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>162755</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H93" t="n">
+        <v>5582</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>EMS S/A</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>69</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>161743</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H94" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>167.73</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>46</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>126215</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H95" t="n">
+        <v>30063</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>HIGIE-PLUS COTTONBABY IND.</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>69</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>161316</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H96" t="n">
+        <v>796383</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>147</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>17590</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H97" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>147</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>19615</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H98" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>39</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>160813</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H99" t="n">
+        <v>789423</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>120</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>156003</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H100" t="n">
+        <v>794365</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>92.09</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>120</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>156004</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H101" t="n">
+        <v>794365</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>106</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>47198</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H102" t="n">
+        <v>31305</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>LABORATORIO GLOBO LTDA</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>152.47</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>147</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>141406</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H103" t="n">
+        <v>31305</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>LABORATORIO GLOBO LTDA</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>145</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>140278</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H104" t="n">
+        <v>793056</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>4562.85</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>39</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>160535</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H105" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>136624</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H106" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>183.84</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>69</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>137009</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H107" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>1811.65</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>69</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>163046</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H108" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>859.64</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>69</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>158379</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H109" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>113.16</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>69</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>158387</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H110" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>135.44</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>69</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>153947</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H111" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>662.5</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>106</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>84018</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H112" t="n">
+        <v>33928</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>39</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>140745</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H113" t="n">
+        <v>789423</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>120</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>139919</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H114" t="n">
+        <v>794365</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>46</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>135423</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H115" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>100</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>161940</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H116" t="n">
+        <v>789603</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>SOFTYS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>106</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>160714</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H117" t="n">
+        <v>31267</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>283.09</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>69</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>152312</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H118" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>157509</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H119" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
         <v>1020.8</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>46</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>156645</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H120" t="n">
+        <v>795345</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>153948</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H121" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>260.32</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>39</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>156161</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H122" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>39</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>156162</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H123" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>125</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FERNANDO NOBRE MARTINS</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>155041</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H124" t="n">
+        <v>792141</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>549.5599999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>125</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>FERNANDO NOBRE MARTINS</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>160304</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H125" t="n">
+        <v>792141</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>163.29</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>147</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>19623</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H126" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>39</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>105538</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H127" t="n">
+        <v>789423</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>46</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>155645</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H128" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>46</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>163433</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H129" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>147</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>86690</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H130" t="n">
+        <v>793186</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>ACCUMED PRODUTOS MEDICO HOSPITALARES LTDA</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>215.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>120</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>154952</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H131" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>39</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>160534</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H132" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="K132" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/vadas.xlsx
+++ b/data/vadas.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,19 +529,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>140629</v>
+        <v>136632</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>95.92</v>
+        <v>188.69</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>152311</v>
+        <v>140457</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>522.64</v>
+        <v>95.55</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -607,15 +607,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>157510</v>
+        <v>140629</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1276</v>
+        <v>95.92</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>163047</v>
+        <v>152311</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>859.64</v>
+        <v>522.64</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -677,19 +677,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>161253</v>
+        <v>156112</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -697,15 +697,15 @@
         <v>46274</v>
       </c>
       <c r="H7" t="n">
-        <v>795345</v>
+        <v>30307</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17.18</v>
+        <v>161.44</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>158354</v>
+        <v>156113</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -734,15 +734,15 @@
         <v>46274</v>
       </c>
       <c r="H8" t="n">
-        <v>139553</v>
+        <v>30307</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>188.12</v>
+        <v>161.44</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>153947</v>
+        <v>157510</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -771,15 +771,15 @@
         <v>46274</v>
       </c>
       <c r="H9" t="n">
-        <v>794319</v>
+        <v>30307</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>260.32</v>
+        <v>1276</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>156161</v>
+        <v>163047</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -808,15 +808,15 @@
         <v>46274</v>
       </c>
       <c r="H10" t="n">
-        <v>794319</v>
+        <v>30307</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>648.98</v>
+        <v>859.64</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -825,19 +825,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>156163</v>
+        <v>136905</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -845,15 +845,15 @@
         <v>46274</v>
       </c>
       <c r="H11" t="n">
-        <v>794319</v>
+        <v>796414</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71.94</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>161744</v>
+        <v>152145</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -882,15 +882,15 @@
         <v>46274</v>
       </c>
       <c r="H12" t="n">
-        <v>794319</v>
+        <v>796414</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>503.19</v>
+        <v>63</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -899,19 +899,19 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>105180</v>
+        <v>161251</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -919,15 +919,15 @@
         <v>46274</v>
       </c>
       <c r="H13" t="n">
-        <v>33928</v>
+        <v>795345</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>69.93000000000001</v>
+        <v>10.98</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -936,19 +936,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>82678</v>
+        <v>161253</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -956,15 +956,15 @@
         <v>46274</v>
       </c>
       <c r="H14" t="n">
-        <v>47252</v>
+        <v>795345</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>21.39</v>
+        <v>17.18</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -973,19 +973,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>154945</v>
+        <v>158354</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -993,15 +993,15 @@
         <v>46274</v>
       </c>
       <c r="H15" t="n">
-        <v>794365</v>
+        <v>139553</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>69.18000000000001</v>
+        <v>188.12</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1010,19 +1010,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>161407</v>
+        <v>153947</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
@@ -1030,15 +1030,15 @@
         <v>46274</v>
       </c>
       <c r="H16" t="n">
-        <v>794365</v>
+        <v>794319</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24.26</v>
+        <v>260.32</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>161804</v>
+        <v>156161</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -1067,15 +1067,15 @@
         <v>46274</v>
       </c>
       <c r="H17" t="n">
-        <v>796496</v>
+        <v>794319</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MAXI CONFORT IMPORTACAO E EXPORTACAO LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>341.34</v>
+        <v>1297.96</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>138992</v>
+        <v>156163</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -1104,15 +1104,15 @@
         <v>46274</v>
       </c>
       <c r="H18" t="n">
-        <v>791717</v>
+        <v>794319</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>28.98</v>
+        <v>71.94</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1121,19 +1121,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>138993</v>
+        <v>161744</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1141,15 +1141,15 @@
         <v>46274</v>
       </c>
       <c r="H19" t="n">
-        <v>791717</v>
+        <v>794319</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>28.98</v>
+        <v>838.65</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1158,19 +1158,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>118990</v>
+        <v>105180</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -1178,15 +1178,15 @@
         <v>46274</v>
       </c>
       <c r="H20" t="n">
-        <v>33057</v>
+        <v>33928</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NATULAB LABORATORIO LTDA</t>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>116.23</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1195,19 +1195,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>155661</v>
+        <v>162972</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -1215,15 +1215,15 @@
         <v>46274</v>
       </c>
       <c r="H21" t="n">
-        <v>794671</v>
+        <v>796383</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>40.27</v>
+        <v>79.45</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1232,19 +1232,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>160026</v>
+        <v>82678</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
@@ -1252,15 +1252,15 @@
         <v>46274</v>
       </c>
       <c r="H22" t="n">
-        <v>794671</v>
+        <v>47252</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>39.26</v>
+        <v>21.39</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>139894</v>
+        <v>139390</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1289,15 +1289,15 @@
         <v>46274</v>
       </c>
       <c r="H23" t="n">
-        <v>789525</v>
+        <v>47252</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>26.7</v>
+        <v>168.59</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1306,19 +1306,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19054</v>
+        <v>154945</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -1326,15 +1326,15 @@
         <v>46274</v>
       </c>
       <c r="H24" t="n">
-        <v>2378</v>
+        <v>794365</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>BELFAR LTDA</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6.47</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1343,19 +1343,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>136623</v>
+        <v>161407</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
@@ -1363,15 +1363,15 @@
         <v>46274</v>
       </c>
       <c r="H25" t="n">
-        <v>30307</v>
+        <v>794365</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>183.84</v>
+        <v>24.26</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>136630</v>
+        <v>130906</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
@@ -1400,15 +1400,15 @@
         <v>46274</v>
       </c>
       <c r="H26" t="n">
-        <v>30307</v>
+        <v>30083</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>205.56</v>
+        <v>6.29</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1417,19 +1417,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>157509</v>
+        <v>133951</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -1437,15 +1437,15 @@
         <v>46274</v>
       </c>
       <c r="H27" t="n">
-        <v>30307</v>
+        <v>30083</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>259.97</v>
+        <v>26.22</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1454,19 +1454,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>163048</v>
+        <v>141058</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
@@ -1474,15 +1474,15 @@
         <v>46274</v>
       </c>
       <c r="H28" t="n">
-        <v>30307</v>
+        <v>30083</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1203.5</v>
+        <v>7.59</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>156646</v>
+        <v>145837</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
@@ -1511,15 +1511,15 @@
         <v>46274</v>
       </c>
       <c r="H29" t="n">
-        <v>795345</v>
+        <v>30083</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>27.3</v>
+        <v>11.09</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1528,19 +1528,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>158356</v>
+        <v>153048</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
@@ -1548,15 +1548,15 @@
         <v>46274</v>
       </c>
       <c r="H30" t="n">
-        <v>139553</v>
+        <v>30083</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1308.39</v>
+        <v>10.39</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>158382</v>
+        <v>161804</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
@@ -1585,15 +1585,15 @@
         <v>46274</v>
       </c>
       <c r="H31" t="n">
-        <v>139553</v>
+        <v>796496</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>MAXI CONFORT IMPORTACAO E EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>339.48</v>
+        <v>341.34</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1602,19 +1602,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>158383</v>
+        <v>145432</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
@@ -1622,15 +1622,15 @@
         <v>46274</v>
       </c>
       <c r="H32" t="n">
-        <v>139553</v>
+        <v>789112</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>MILI SA</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>113.16</v>
+        <v>460.62</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1639,19 +1639,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>158384</v>
+        <v>155793</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
@@ -1659,15 +1659,15 @@
         <v>46274</v>
       </c>
       <c r="H33" t="n">
-        <v>139553</v>
+        <v>789112</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>MILI SA</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>444.52</v>
+        <v>260.91</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1680,15 +1680,15 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>153308</v>
+        <v>138992</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
@@ -1696,15 +1696,15 @@
         <v>46274</v>
       </c>
       <c r="H34" t="n">
-        <v>794319</v>
+        <v>791717</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>101.22</v>
+        <v>28.98</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1713,19 +1713,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>153948</v>
+        <v>138993</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
@@ -1733,15 +1733,15 @@
         <v>46274</v>
       </c>
       <c r="H35" t="n">
-        <v>794319</v>
+        <v>791717</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>927.5</v>
+        <v>28.98</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1750,19 +1750,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>156160</v>
+        <v>162331</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1770,15 +1770,15 @@
         <v>46274</v>
       </c>
       <c r="H36" t="n">
-        <v>794319</v>
+        <v>791717</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>259.59</v>
+        <v>25.78</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1787,19 +1787,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>161314</v>
+        <v>94676</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1807,15 +1807,15 @@
         <v>46274</v>
       </c>
       <c r="H37" t="n">
-        <v>796383</v>
+        <v>33057</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>14</v>
+        <v>43.29</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1824,19 +1824,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>134701</v>
+        <v>94722</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1844,15 +1844,15 @@
         <v>46274</v>
       </c>
       <c r="H38" t="n">
-        <v>789423</v>
+        <v>33057</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>23.3</v>
+        <v>42.63</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1861,19 +1861,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>145830</v>
+        <v>118990</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
@@ -1881,15 +1881,15 @@
         <v>46274</v>
       </c>
       <c r="H39" t="n">
-        <v>30083</v>
+        <v>33057</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>18.59</v>
+        <v>116.23</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>130133</v>
+        <v>155661</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1918,15 +1918,15 @@
         <v>46274</v>
       </c>
       <c r="H40" t="n">
-        <v>791717</v>
+        <v>794671</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>19.58</v>
+        <v>281.89</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>158566</v>
+        <v>160026</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>51.65</v>
+        <v>39.26</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -1976,15 +1976,15 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>136634</v>
+        <v>143460</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -1992,15 +1992,15 @@
         <v>46274</v>
       </c>
       <c r="H42" t="n">
-        <v>30307</v>
+        <v>790595</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>SC JOHNSON LTDA</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>616.6799999999999</v>
+        <v>54.45</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2009,19 +2009,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>157509</v>
+        <v>139894</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
@@ -2029,15 +2029,15 @@
         <v>46274</v>
       </c>
       <c r="H43" t="n">
-        <v>30307</v>
+        <v>789525</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>119.96</v>
+        <v>26.7</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2046,19 +2046,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>161254</v>
+        <v>19054</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
@@ -2066,15 +2066,15 @@
         <v>46274</v>
       </c>
       <c r="H44" t="n">
-        <v>795345</v>
+        <v>2378</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>BELFAR LTDA</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>40.5</v>
+        <v>6.47</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2083,19 +2083,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>155035</v>
+        <v>136623</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
@@ -2103,15 +2103,15 @@
         <v>46274</v>
       </c>
       <c r="H45" t="n">
-        <v>792141</v>
+        <v>30307</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>221.66</v>
+        <v>183.84</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2120,19 +2120,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>27723</v>
+        <v>136630</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
@@ -2140,15 +2140,15 @@
         <v>46274</v>
       </c>
       <c r="H46" t="n">
-        <v>789423</v>
+        <v>30307</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>28.19</v>
+        <v>205.56</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2161,15 +2161,15 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>162451</v>
+        <v>140514</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -2177,15 +2177,15 @@
         <v>46274</v>
       </c>
       <c r="H47" t="n">
-        <v>789423</v>
+        <v>30307</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>14</v>
+        <v>188.69</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2194,19 +2194,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>156187</v>
+        <v>157509</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
@@ -2214,15 +2214,15 @@
         <v>46274</v>
       </c>
       <c r="H48" t="n">
-        <v>794365</v>
+        <v>30307</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>77.83</v>
+        <v>259.97</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2231,19 +2231,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>139826</v>
+        <v>163048</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2251,15 +2251,15 @@
         <v>46274</v>
       </c>
       <c r="H49" t="n">
-        <v>30083</v>
+        <v>30307</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>36.18</v>
+        <v>1203.5</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>144874</v>
+        <v>156646</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -2288,15 +2288,15 @@
         <v>46274</v>
       </c>
       <c r="H50" t="n">
-        <v>30083</v>
+        <v>795345</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>14.99</v>
+        <v>27.3</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2305,19 +2305,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>148254</v>
+        <v>158356</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
@@ -2325,15 +2325,15 @@
         <v>46274</v>
       </c>
       <c r="H51" t="n">
-        <v>789112</v>
+        <v>139553</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MILI SA</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>152.91</v>
+        <v>2616.78</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2342,19 +2342,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>139215</v>
+        <v>158382</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -2362,15 +2362,15 @@
         <v>46274</v>
       </c>
       <c r="H52" t="n">
-        <v>793056</v>
+        <v>139553</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>14142.51</v>
+        <v>452.64</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>160129</v>
+        <v>158383</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
@@ -2399,15 +2399,15 @@
         <v>46274</v>
       </c>
       <c r="H53" t="n">
-        <v>795898</v>
+        <v>139553</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>VIDA FORTE NUTRIENTES INDUSTRIA E COMERCIO DE PRODUTOS NATUR</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>264.68</v>
+        <v>113.16</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2416,19 +2416,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>137009</v>
+        <v>158384</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
@@ -2436,15 +2436,15 @@
         <v>46274</v>
       </c>
       <c r="H54" t="n">
-        <v>30307</v>
+        <v>139553</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>822.24</v>
+        <v>444.52</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2457,15 +2457,15 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>156643</v>
+        <v>153308</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -2473,15 +2473,15 @@
         <v>46274</v>
       </c>
       <c r="H55" t="n">
-        <v>795345</v>
+        <v>794319</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>23.7</v>
+        <v>101.22</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>158352</v>
+        <v>153948</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -2510,15 +2510,15 @@
         <v>46274</v>
       </c>
       <c r="H56" t="n">
-        <v>139553</v>
+        <v>794319</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>188.12</v>
+        <v>2517.51</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2531,15 +2531,15 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>158363</v>
+        <v>156160</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
@@ -2547,15 +2547,15 @@
         <v>46274</v>
       </c>
       <c r="H57" t="n">
-        <v>139553</v>
+        <v>794319</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1308.39</v>
+        <v>259.59</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2568,15 +2568,15 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>153947</v>
+        <v>156163</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1192.5</v>
+        <v>75.44</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2601,19 +2601,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>92525</v>
+        <v>161314</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
@@ -2621,15 +2621,15 @@
         <v>46274</v>
       </c>
       <c r="H59" t="n">
-        <v>47252</v>
+        <v>796383</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>29.21</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2638,19 +2638,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>161408</v>
+        <v>134701</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -2658,15 +2658,15 @@
         <v>46274</v>
       </c>
       <c r="H60" t="n">
-        <v>794365</v>
+        <v>789423</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>40.01</v>
+        <v>23.3</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2675,19 +2675,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>139826</v>
+        <v>132622</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>18.59</v>
+        <v>26.38</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>140453</v>
+        <v>139815</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>9.789999999999999</v>
+        <v>17.97</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>141132</v>
+        <v>144315</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
@@ -2769,15 +2769,15 @@
         <v>46274</v>
       </c>
       <c r="H63" t="n">
-        <v>789112</v>
+        <v>30083</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MILI SA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>260.91</v>
+        <v>21.78</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2786,19 +2786,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>162363</v>
+        <v>145830</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
@@ -2806,15 +2806,15 @@
         <v>46274</v>
       </c>
       <c r="H64" t="n">
-        <v>791717</v>
+        <v>30083</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>18.78</v>
+        <v>18.59</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>144229</v>
+        <v>145838</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
@@ -2843,15 +2843,15 @@
         <v>46274</v>
       </c>
       <c r="H65" t="n">
-        <v>789603</v>
+        <v>30083</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SOFTYS BRASIL LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>206.94</v>
+        <v>11.09</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2860,19 +2860,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>74535</v>
+        <v>159256</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
@@ -2880,15 +2880,15 @@
         <v>46274</v>
       </c>
       <c r="H66" t="n">
-        <v>789525</v>
+        <v>30083</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>44.87</v>
+        <v>24.62</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -2897,19 +2897,19 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>74616</v>
+        <v>160604</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
@@ -2917,15 +2917,15 @@
         <v>46274</v>
       </c>
       <c r="H67" t="n">
-        <v>789525</v>
+        <v>30083</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>123.78</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -2934,19 +2934,19 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>74713</v>
+        <v>141151</v>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
@@ -2954,15 +2954,15 @@
         <v>46274</v>
       </c>
       <c r="H68" t="n">
-        <v>789525</v>
+        <v>789112</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>MILI SA</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>58.13</v>
+        <v>89.59</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -2971,19 +2971,19 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>139738</v>
+        <v>130133</v>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
@@ -2991,15 +2991,15 @@
         <v>46274</v>
       </c>
       <c r="H69" t="n">
-        <v>789525</v>
+        <v>791717</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>87.69</v>
+        <v>19.58</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3008,19 +3008,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>139929</v>
+        <v>158566</v>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
@@ -3028,15 +3028,15 @@
         <v>46274</v>
       </c>
       <c r="H70" t="n">
-        <v>789525</v>
+        <v>794671</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>41.5</v>
+        <v>154.95</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3045,19 +3045,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>154932</v>
+        <v>153227</v>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
@@ -3065,15 +3065,15 @@
         <v>46274</v>
       </c>
       <c r="H71" t="n">
-        <v>789525</v>
+        <v>790595</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>SC JOHNSON LTDA</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>13.31</v>
+        <v>72.09</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>136633</v>
+        <v>157241</v>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
@@ -3102,15 +3102,15 @@
         <v>46274</v>
       </c>
       <c r="H72" t="n">
-        <v>30307</v>
+        <v>789603</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>SOFTYS BRASIL LTDA</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>330</v>
+        <v>29.56</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3119,19 +3119,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>157510</v>
+        <v>141707</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
@@ -3139,15 +3139,15 @@
         <v>46274</v>
       </c>
       <c r="H73" t="n">
-        <v>30307</v>
+        <v>794029</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>WELLA BRASIL LTDA</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>389.95</v>
+        <v>59.67</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3156,19 +3156,19 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>158351</v>
+        <v>155828</v>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
@@ -3176,15 +3176,15 @@
         <v>46274</v>
       </c>
       <c r="H74" t="n">
-        <v>139553</v>
+        <v>789470</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>BASTON INDUSTRIA DE AEROSSOIS LTDA</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>376.24</v>
+        <v>11.36</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>158385</v>
+        <v>136633</v>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
@@ -3213,15 +3213,15 @@
         <v>46274</v>
       </c>
       <c r="H75" t="n">
-        <v>139553</v>
+        <v>30307</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2310.65</v>
+        <v>188.69</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3230,19 +3230,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>156160</v>
+        <v>136634</v>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
@@ -3250,15 +3250,15 @@
         <v>46274</v>
       </c>
       <c r="H76" t="n">
-        <v>794319</v>
+        <v>30307</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1038.37</v>
+        <v>616.6799999999999</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3267,19 +3267,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>58920</v>
+        <v>140516</v>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
@@ -3287,15 +3287,15 @@
         <v>46274</v>
       </c>
       <c r="H77" t="n">
-        <v>793261</v>
+        <v>30307</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>FARMAX DISTRIBUIDORA S.A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>9.800000000000001</v>
+        <v>201.16</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3304,19 +3304,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>149193</v>
+        <v>141164</v>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
@@ -3324,15 +3324,15 @@
         <v>46274</v>
       </c>
       <c r="H78" t="n">
-        <v>793261</v>
+        <v>30307</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>FARMAX DISTRIBUIDORA S.A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>10.05</v>
+        <v>95.55</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>155198</v>
+        <v>156109</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
@@ -3361,15 +3361,15 @@
         <v>46274</v>
       </c>
       <c r="H79" t="n">
-        <v>792141</v>
+        <v>30307</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>366.49</v>
+        <v>322.88</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3378,19 +3378,19 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>157689</v>
+        <v>157509</v>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
@@ -3398,15 +3398,15 @@
         <v>46274</v>
       </c>
       <c r="H80" t="n">
-        <v>792141</v>
+        <v>30307</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>196.08</v>
+        <v>119.96</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3415,19 +3415,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>79243</v>
+        <v>158058</v>
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
@@ -3435,15 +3435,15 @@
         <v>46274</v>
       </c>
       <c r="H81" t="n">
-        <v>47252</v>
+        <v>795345</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>11.47</v>
+        <v>92.94</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3452,19 +3452,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>139737</v>
+        <v>161254</v>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
@@ -3472,15 +3472,15 @@
         <v>46274</v>
       </c>
       <c r="H82" t="n">
-        <v>794365</v>
+        <v>795345</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>82</v>
+        <v>40.5</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3489,19 +3489,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>RILARY DIENIFER TRAUTMANN LIMA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>143167</v>
+        <v>158389</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
@@ -3509,15 +3509,15 @@
         <v>46274</v>
       </c>
       <c r="H83" t="n">
-        <v>30791</v>
+        <v>139553</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>37.51</v>
+        <v>377.94</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3530,15 +3530,15 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>FERNANDO NOBRE MARTINS</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>146414</v>
+        <v>155035</v>
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
@@ -3546,15 +3546,15 @@
         <v>46274</v>
       </c>
       <c r="H84" t="n">
-        <v>33286</v>
+        <v>792141</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>33.97</v>
+        <v>221.66</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3563,19 +3563,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>160521</v>
+        <v>161327</v>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -3583,15 +3583,15 @@
         <v>46274</v>
       </c>
       <c r="H85" t="n">
-        <v>794671</v>
+        <v>796383</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>32.93</v>
+        <v>70.45</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3600,19 +3600,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>139926</v>
+        <v>27723</v>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
@@ -3620,15 +3620,15 @@
         <v>46274</v>
       </c>
       <c r="H86" t="n">
-        <v>789525</v>
+        <v>789423</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>72.63</v>
+        <v>28.19</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3637,19 +3637,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>139951</v>
+        <v>162451</v>
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
@@ -3657,15 +3657,15 @@
         <v>46274</v>
       </c>
       <c r="H87" t="n">
-        <v>789525</v>
+        <v>789423</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>55.41</v>
+        <v>14</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>159933</v>
+        <v>156187</v>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
@@ -3694,15 +3694,15 @@
         <v>46274</v>
       </c>
       <c r="H88" t="n">
-        <v>789525</v>
+        <v>794365</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>30</v>
+        <v>77.83</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3715,15 +3715,15 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>136622</v>
+        <v>134991</v>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
@@ -3731,15 +3731,15 @@
         <v>46274</v>
       </c>
       <c r="H89" t="n">
-        <v>30307</v>
+        <v>30083</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>183.84</v>
+        <v>7.19</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3748,19 +3748,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>163049</v>
+        <v>139826</v>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
@@ -3768,15 +3768,15 @@
         <v>46274</v>
       </c>
       <c r="H90" t="n">
-        <v>30307</v>
+        <v>30083</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1203.5</v>
+        <v>36.18</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3797,7 +3797,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>161249</v>
+        <v>144032</v>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -3805,15 +3805,15 @@
         <v>46274</v>
       </c>
       <c r="H91" t="n">
-        <v>795345</v>
+        <v>30083</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>23.7</v>
+        <v>24.23</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>161256</v>
+        <v>144316</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
@@ -3842,15 +3842,15 @@
         <v>46274</v>
       </c>
       <c r="H92" t="n">
-        <v>795345</v>
+        <v>30083</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>24.3</v>
+        <v>10.89</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -3859,19 +3859,19 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>162755</v>
+        <v>144874</v>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
@@ -3879,15 +3879,15 @@
         <v>46274</v>
       </c>
       <c r="H93" t="n">
-        <v>5582</v>
+        <v>30083</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>EMS S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>27.9</v>
+        <v>14.99</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -3896,19 +3896,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>161743</v>
+        <v>145843</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
@@ -3916,15 +3916,15 @@
         <v>46274</v>
       </c>
       <c r="H94" t="n">
-        <v>794319</v>
+        <v>30083</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>167.73</v>
+        <v>40.38</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>126215</v>
+        <v>148254</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
@@ -3953,15 +3953,15 @@
         <v>46274</v>
       </c>
       <c r="H95" t="n">
-        <v>30063</v>
+        <v>789112</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>HIGIE-PLUS COTTONBABY IND.</t>
+          <t>MILI SA</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>23.88</v>
+        <v>305.82</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -3970,19 +3970,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>161316</v>
+        <v>94650</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
@@ -3990,15 +3990,15 @@
         <v>46274</v>
       </c>
       <c r="H96" t="n">
-        <v>796383</v>
+        <v>33057</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+          <t>NATULAB LABORATORIO LTDA</t>
         </is>
       </c>
       <c r="J96" t="n">
-        <v>9.33</v>
+        <v>43.3</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4007,19 +4007,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>17590</v>
+        <v>139215</v>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
@@ -4027,15 +4027,15 @@
         <v>46274</v>
       </c>
       <c r="H97" t="n">
-        <v>47252</v>
+        <v>793056</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>25.9</v>
+        <v>14142.51</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4044,19 +4044,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>19615</v>
+        <v>160129</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
@@ -4064,15 +4064,15 @@
         <v>46274</v>
       </c>
       <c r="H98" t="n">
-        <v>47252</v>
+        <v>795898</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>VIDA FORTE NUTRIENTES INDUSTRIA E COMERCIO DE PRODUTOS NATUR</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>9.4</v>
+        <v>264.68</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4085,15 +4085,15 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>160813</v>
+        <v>136624</v>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
@@ -4101,15 +4101,15 @@
         <v>46274</v>
       </c>
       <c r="H99" t="n">
-        <v>789423</v>
+        <v>30307</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>32.82</v>
+        <v>251.5</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4118,19 +4118,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>156003</v>
+        <v>137009</v>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
@@ -4138,15 +4138,15 @@
         <v>46274</v>
       </c>
       <c r="H100" t="n">
-        <v>794365</v>
+        <v>30307</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>92.09</v>
+        <v>822.24</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4155,19 +4155,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>156004</v>
+        <v>156643</v>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
@@ -4175,15 +4175,15 @@
         <v>46274</v>
       </c>
       <c r="H101" t="n">
-        <v>794365</v>
+        <v>795345</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>137.93</v>
+        <v>23.7</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4192,19 +4192,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>47198</v>
+        <v>161253</v>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
@@ -4212,15 +4212,15 @@
         <v>46274</v>
       </c>
       <c r="H102" t="n">
-        <v>31305</v>
+        <v>795345</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>LABORATORIO GLOBO LTDA</t>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
         </is>
       </c>
       <c r="J102" t="n">
-        <v>152.47</v>
+        <v>33.6</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4229,19 +4229,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>141406</v>
+        <v>158352</v>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
@@ -4249,15 +4249,15 @@
         <v>46274</v>
       </c>
       <c r="H103" t="n">
-        <v>31305</v>
+        <v>139553</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>LABORATORIO GLOBO LTDA</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>16.21</v>
+        <v>376.24</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4266,19 +4266,19 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>140278</v>
+        <v>158363</v>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
@@ -4286,15 +4286,15 @@
         <v>46274</v>
       </c>
       <c r="H104" t="n">
-        <v>793056</v>
+        <v>139553</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
         </is>
       </c>
       <c r="J104" t="n">
-        <v>4562.85</v>
+        <v>2616.78</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>160535</v>
+        <v>153947</v>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
@@ -4323,15 +4323,15 @@
         <v>46274</v>
       </c>
       <c r="H105" t="n">
-        <v>789525</v>
+        <v>794319</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J105" t="n">
-        <v>49.39</v>
+        <v>1192.5</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4340,19 +4340,19 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>136624</v>
+        <v>156162</v>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
@@ -4360,15 +4360,15 @@
         <v>46274</v>
       </c>
       <c r="H106" t="n">
-        <v>30307</v>
+        <v>794319</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>183.84</v>
+        <v>449.82</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>137009</v>
+        <v>161328</v>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
@@ -4397,15 +4397,15 @@
         <v>46274</v>
       </c>
       <c r="H107" t="n">
-        <v>30307</v>
+        <v>796383</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
         </is>
       </c>
       <c r="J107" t="n">
-        <v>1811.65</v>
+        <v>52.09</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4414,19 +4414,19 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>163046</v>
+        <v>92525</v>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
@@ -4434,15 +4434,15 @@
         <v>46274</v>
       </c>
       <c r="H108" t="n">
-        <v>30307</v>
+        <v>47252</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>HYPERA S.A</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>859.64</v>
+        <v>29.21</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4451,19 +4451,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>158379</v>
+        <v>161408</v>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
@@ -4471,15 +4471,15 @@
         <v>46274</v>
       </c>
       <c r="H109" t="n">
-        <v>139553</v>
+        <v>794365</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>113.16</v>
+        <v>40.01</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4488,19 +4488,19 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>158387</v>
+        <v>126927</v>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
@@ -4508,15 +4508,15 @@
         <v>46274</v>
       </c>
       <c r="H110" t="n">
-        <v>139553</v>
+        <v>30083</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>135.44</v>
+        <v>8.18</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4525,19 +4525,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>153947</v>
+        <v>126939</v>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
@@ -4545,15 +4545,15 @@
         <v>46274</v>
       </c>
       <c r="H111" t="n">
-        <v>794319</v>
+        <v>30083</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>662.5</v>
+        <v>6.89</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4562,19 +4562,19 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>84018</v>
+        <v>134126</v>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
@@ -4582,15 +4582,15 @@
         <v>46274</v>
       </c>
       <c r="H112" t="n">
-        <v>33928</v>
+        <v>30083</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>GEOLAB IND FARMACEUTICA S/A</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>52.4</v>
+        <v>18.39</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4599,19 +4599,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>140745</v>
+        <v>139826</v>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
@@ -4619,15 +4619,15 @@
         <v>46274</v>
       </c>
       <c r="H113" t="n">
-        <v>789423</v>
+        <v>30083</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J113" t="n">
-        <v>20.01</v>
+        <v>18.59</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4636,19 +4636,19 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>139919</v>
+        <v>140453</v>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
@@ -4656,15 +4656,15 @@
         <v>46274</v>
       </c>
       <c r="H114" t="n">
-        <v>794365</v>
+        <v>30083</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>14.89</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>135423</v>
+        <v>145840</v>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>19.59</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4710,19 +4710,19 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>161940</v>
+        <v>153050</v>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
@@ -4730,15 +4730,15 @@
         <v>46274</v>
       </c>
       <c r="H116" t="n">
-        <v>789603</v>
+        <v>30083</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SOFTYS BRASIL LTDA</t>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>116.64</v>
+        <v>26.97</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4747,19 +4747,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JOSE MARIA FERNANDES FONTENELE</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>160714</v>
+        <v>141132</v>
       </c>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
@@ -4767,15 +4767,15 @@
         <v>46274</v>
       </c>
       <c r="H117" t="n">
-        <v>31267</v>
+        <v>789112</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+          <t>MILI SA</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>283.09</v>
+        <v>260.91</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -4784,19 +4784,19 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>152312</v>
+        <v>162363</v>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
@@ -4804,15 +4804,15 @@
         <v>46274</v>
       </c>
       <c r="H118" t="n">
-        <v>30307</v>
+        <v>791717</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>348.43</v>
+        <v>18.78</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -4825,15 +4825,15 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>157509</v>
+        <v>155641</v>
       </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
@@ -4841,15 +4841,15 @@
         <v>46274</v>
       </c>
       <c r="H119" t="n">
-        <v>30307</v>
+        <v>794671</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>1020.8</v>
+        <v>103.3</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>156645</v>
+        <v>144229</v>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
@@ -4878,15 +4878,15 @@
         <v>46274</v>
       </c>
       <c r="H120" t="n">
-        <v>795345</v>
+        <v>789603</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+          <t>SOFTYS BRASIL LTDA</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>24.3</v>
+        <v>206.94</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -4895,19 +4895,19 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SALDANHA JUNIOR</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>153948</v>
+        <v>74535</v>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
@@ -4915,15 +4915,15 @@
         <v>46274</v>
       </c>
       <c r="H121" t="n">
-        <v>794319</v>
+        <v>789525</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>260.32</v>
+        <v>44.87</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -4932,19 +4932,19 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>39</v>
+        <v>120</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>156161</v>
+        <v>74616</v>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
@@ -4952,15 +4952,15 @@
         <v>46274</v>
       </c>
       <c r="H122" t="n">
-        <v>794319</v>
+        <v>789525</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J122" t="n">
-        <v>129.8</v>
+        <v>123.78</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -4981,7 +4981,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>156162</v>
+        <v>74713</v>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
@@ -4989,15 +4989,15 @@
         <v>46274</v>
       </c>
       <c r="H123" t="n">
-        <v>794319</v>
+        <v>789525</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>199.92</v>
+        <v>58.13</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5006,19 +5006,19 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>155041</v>
+        <v>139738</v>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
@@ -5026,15 +5026,15 @@
         <v>46274</v>
       </c>
       <c r="H124" t="n">
-        <v>792141</v>
+        <v>789525</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>549.5599999999999</v>
+        <v>87.69</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5043,19 +5043,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FERNANDO NOBRE MARTINS</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>160304</v>
+        <v>139929</v>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
@@ -5063,15 +5063,15 @@
         <v>46274</v>
       </c>
       <c r="H125" t="n">
-        <v>792141</v>
+        <v>789525</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>163.29</v>
+        <v>41.5</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5080,19 +5080,19 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>19623</v>
+        <v>154932</v>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
@@ -5100,15 +5100,15 @@
         <v>46274</v>
       </c>
       <c r="H126" t="n">
-        <v>47252</v>
+        <v>789525</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>HYPERA S.A</t>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>25.98</v>
+        <v>13.31</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5117,19 +5117,19 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>105538</v>
+        <v>153309</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
@@ -5137,15 +5137,15 @@
         <v>46274</v>
       </c>
       <c r="H127" t="n">
-        <v>789423</v>
+        <v>30105</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+          <t>ALYNE - CIGEL DISTRIBUIDORA DE COSMETI</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>28.44</v>
+        <v>13.34</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5158,15 +5158,15 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>SALDANHA JUNIOR</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>155645</v>
+        <v>136633</v>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
@@ -5174,15 +5174,15 @@
         <v>46274</v>
       </c>
       <c r="H128" t="n">
-        <v>794671</v>
+        <v>30307</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>41.16</v>
+        <v>330</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5191,19 +5191,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>163433</v>
+        <v>136635</v>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
@@ -5211,15 +5211,15 @@
         <v>46274</v>
       </c>
       <c r="H129" t="n">
-        <v>794671</v>
+        <v>30307</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>91.18000000000001</v>
+        <v>188.69</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5228,19 +5228,19 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>86690</v>
+        <v>156110</v>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
@@ -5248,15 +5248,15 @@
         <v>46274</v>
       </c>
       <c r="H130" t="n">
-        <v>793186</v>
+        <v>30307</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>ACCUMED PRODUTOS MEDICO HOSPITALARES LTDA</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>215.96</v>
+        <v>161.44</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5265,19 +5265,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>154952</v>
+        <v>157510</v>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
@@ -5285,15 +5285,15 @@
         <v>46274</v>
       </c>
       <c r="H131" t="n">
-        <v>789525</v>
+        <v>30307</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>14.8</v>
+        <v>389.95</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5306,15 +5306,15 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>160534</v>
+        <v>136888</v>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
@@ -5322,17 +5322,3754 @@
         <v>46274</v>
       </c>
       <c r="H132" t="n">
+        <v>796414</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>69</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>140693</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H133" t="n">
+        <v>796414</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>47.51</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>69</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>158351</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H134" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>69</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>158385</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H135" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>2977.43</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>114</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>RILARY DIENIFER TRAUTMANN LIMA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>158387</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H136" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>269.52</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>69</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>156160</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H137" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>2336.33</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>147</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>58920</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H138" t="n">
+        <v>793261</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>FARMAX DISTRIBUIDORA S.A</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>147</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>149193</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H139" t="n">
+        <v>793261</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>FARMAX DISTRIBUIDORA S.A</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>46</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>134235</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H140" t="n">
+        <v>792121</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>GIOVANNA BABY - PRO NOVA DIST E COM DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>125</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FERNANDO NOBRE MARTINS</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>155198</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H141" t="n">
+        <v>792141</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>366.49</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>125</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>FERNANDO NOBRE MARTINS</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>157689</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H142" t="n">
+        <v>792141</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>69</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>161329</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H143" t="n">
+        <v>796383</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>147</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>79243</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H144" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>120</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>139737</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H145" t="n">
+        <v>794365</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>82</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>120</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>86649</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H146" t="n">
+        <v>30791</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>341.03</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>106</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>143167</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H147" t="n">
+        <v>30791</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>LABORATORIO TEUTO BRASILEIRO S/A</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>46</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>135347</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H148" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>46</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>156164</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H149" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>37.58</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>46</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>159390</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H150" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>106</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>146414</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H151" t="n">
+        <v>33286</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>MULTILAB IND E COM DE PROD FARMAC LTDA (MARCAS)</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>120</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>94668</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H152" t="n">
+        <v>33057</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>NATULAB LABORATORIO LTDA</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>46</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>160521</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H153" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>46</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>143437</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H154" t="n">
+        <v>790595</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>SC JOHNSON LTDA</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>46</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>141709</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H155" t="n">
+        <v>794029</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>WELLA BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>120</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>139926</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H156" t="n">
         <v>789525</v>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I156" t="inlineStr">
         <is>
           <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
         </is>
       </c>
-      <c r="J132" t="n">
+      <c r="J156" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>120</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>139951</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H157" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>120</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>159933</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H158" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>30</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>2</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>136622</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H159" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>183.84</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>69</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>163049</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H160" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>1203.5</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>46</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>161249</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H161" t="n">
+        <v>795345</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>46</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>161256</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H162" t="n">
+        <v>795345</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>114</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>RILARY DIENIFER TRAUTMANN LIMA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>158388</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H163" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>269.52</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>114</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>RILARY DIENIFER TRAUTMANN LIMA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>158390</v>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H164" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>377.94</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>39</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>162755</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H165" t="n">
+        <v>5582</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>EMS S/A</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>69</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>161743</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H166" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>167.73</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>46</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>148453</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H167" t="n">
+        <v>792121</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>GIOVANNA BABY - PRO NOVA DIST E COM DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>46</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>126215</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H168" t="n">
+        <v>30063</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>HIGIE-PLUS COTTONBABY IND.</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>69</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>134369</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H169" t="n">
+        <v>30063</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>HIGIE-PLUS COTTONBABY IND.</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>69</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>161316</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H170" t="n">
+        <v>796383</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>147</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>17590</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H171" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>147</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>19615</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H172" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>39</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>160813</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H173" t="n">
+        <v>789423</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>120</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>156003</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H174" t="n">
+        <v>794365</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>92.09</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>120</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>156004</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H175" t="n">
+        <v>794365</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>106</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>47198</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H176" t="n">
+        <v>31305</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>LABORATORIO GLOBO LTDA</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>152.47</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>147</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>141406</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H177" t="n">
+        <v>31305</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>LABORATORIO GLOBO LTDA</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>46</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>130767</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H178" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>46</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>130135</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H179" t="n">
+        <v>791717</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>46</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>130137</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H180" t="n">
+        <v>791717</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>MURIEL - BEAUTY LAB. DO BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>145</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>MATHEUS TEIXEIRA ALVES GASPAR</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>140278</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H181" t="n">
+        <v>793056</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>OPELLA HEALTHCARE BRAZIL LTDA - SANOFI</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>4562.85</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>46</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>155638</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H182" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>46</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>160520</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H183" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>39</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>160535</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H184" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>69</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>136622</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H185" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>69</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>136623</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H186" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>754.49</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>2</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>136624</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H187" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>183.84</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>69</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>136634</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H188" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>452.92</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>69</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>137009</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H189" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>2264.57</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>69</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>163046</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H190" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>859.64</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>69</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>152143</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H191" t="n">
+        <v>796414</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>DENTAL CLEAN -ATLANTIS DISTRIBUIDORA DE PROD DE HIG LTDA</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>63</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>69</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>158379</v>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H192" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>113.16</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>69</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>158387</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H193" t="n">
+        <v>139553</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>DINNO/PLENTY - CCM IND E COM DE PROD DESCART S/A</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>135.44</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>69</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>153947</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H194" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>2915.01</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>106</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>84018</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H195" t="n">
+        <v>33928</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>GEOLAB IND FARMACEUTICA S/A</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>69</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>161323</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H196" t="n">
+        <v>796383</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>HILLO - APERIFIO INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>93.77</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>39</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>140745</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H197" t="n">
+        <v>789423</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>120</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>139919</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H198" t="n">
+        <v>794365</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>LABOFARMA PRODUTOS FARMACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>46</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>135423</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H199" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>46</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>142080</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H200" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>46</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>155634</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H201" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>100</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>WELLINGTON NASCIMENTO SANTOS - HB</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>161940</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H202" t="n">
+        <v>789603</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>SOFTYS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>116.64</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>106</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>JOSE MARIA FERNANDES FONTENELE</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>160714</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H203" t="n">
+        <v>31267</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>MEDQUIMICA IND FARMACEUTICA S.</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>283.09</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>69</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>160314</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H204" t="n">
+        <v>796144</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>BRACELL PAPEIS NORDESTE LTDA</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>210.98</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>69</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>152312</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H205" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>157509</v>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H206" t="n">
+        <v>30307</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>CCM IND E COM DE PROD DESCARTAVEIS S/A</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>1276</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>46</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>156645</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H207" t="n">
+        <v>795345</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>DINNO BABY - DIST DE COSMET BY FATTORE LTDA - EPP</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SALDANHA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>153948</v>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H208" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>260.32</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>39</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>156161</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H209" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>39</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>156162</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H210" t="n">
+        <v>794319</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>EUROFRAL PRODUTOS DE HIGIENE LTDA</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>199.92</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>125</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>FERNANDO NOBRE MARTINS</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>155041</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H211" t="n">
+        <v>792141</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>549.5599999999999</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>125</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>FERNANDO NOBRE MARTINS</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>160304</v>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H212" t="n">
+        <v>792141</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>GROWUP INDUSTRIA DE ALIMENTOS E NUTRACEUTICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>163.29</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>69</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>153929</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H213" t="n">
+        <v>30063</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>HIGIE-PLUS COTTONBABY IND.</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>147</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>19623</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H214" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>120</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>80098</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H215" t="n">
+        <v>47252</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>HYPERA S.A</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>72.28</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>39</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>105538</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H216" t="n">
+        <v>789423</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>KLEY HERTZ DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>46</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>135355</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H217" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>46</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>145835</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H218" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>26.98</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>46</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>155678</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H219" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>46</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>156951</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H220" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>46</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>159388</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H221" t="n">
+        <v>30083</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>LOLLY BABY PRODUTOS INFANTIS L</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>46</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>155645</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H222" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>164.64</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>46</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>159746</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H223" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>65.88</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>46</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>159756</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H224" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>116.76</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>46</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>163433</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H225" t="n">
+        <v>794671</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>PRINCIPIA ES COMERCIO DE COSMETICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J225" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>46</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>146931</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H226" t="n">
+        <v>790595</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>SC JOHNSON LTDA</t>
+        </is>
+      </c>
+      <c r="J226" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>69</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>157234</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H227" t="n">
+        <v>789603</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>SOFTYS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J227" t="n">
+        <v>37.88</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>69</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>EDEVANIA DA SILVA PEREIRA (PLUS)</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>157237</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H228" t="n">
+        <v>789603</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>SOFTYS BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J228" t="n">
+        <v>58.71</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>46</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>160472</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H229" t="n">
+        <v>794029</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>WELLA BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J229" t="n">
+        <v>71.97</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>46</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>VANILTON HOLANDA DA SILVA JUNIOR</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>160481</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H230" t="n">
+        <v>794029</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>WELLA BRASIL LTDA</t>
+        </is>
+      </c>
+      <c r="J230" t="n">
+        <v>71.97</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>147</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ALEXSANDRO P DA VEIGA PACHECO (FARMA PE)</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>86690</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H231" t="n">
+        <v>793186</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>ACCUMED PRODUTOS MEDICO HOSPITALARES LTDA</t>
+        </is>
+      </c>
+      <c r="J231" t="n">
+        <v>215.96</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>120</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>NUBIA EDUARDA DA CRUZ SOUZA</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>154952</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H232" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J232" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>39</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SAYONARA CORDEIRO DA COSTA HOLANDA</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>160534</v>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="H233" t="n">
+        <v>789525</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>ACHE LABORATORIOS FARMACEUTICOS S/A</t>
+        </is>
+      </c>
+      <c r="J233" t="n">
         <v>31.83</v>
       </c>
-      <c r="K132" t="n">
+      <c r="K233" t="n">
         <v>0</v>
       </c>
     </row>
